--- a/experiment/01-BOUNDARY_TEST_ATCC25922.xlsx
+++ b/experiment/01-BOUNDARY_TEST_ATCC25922.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Modeling of Antibiotic Resistance\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9C1796-EE91-4D33-A60E-1FBE4F7A580D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1E52D3-6CD2-45F5-8EA9-3507BB6B24C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44670" yWindow="2865" windowWidth="21600" windowHeight="11175" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1035" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Read me first" sheetId="1" r:id="rId1"/>
-    <sheet name="Design" sheetId="2" r:id="rId2"/>
-    <sheet name="Prediction" sheetId="3" r:id="rId3"/>
-    <sheet name="Counts" sheetId="4" r:id="rId4"/>
-    <sheet name="Day 0 check" sheetId="5" r:id="rId5"/>
+    <sheet name="Design" sheetId="2" r:id="rId1"/>
+    <sheet name="Prediction" sheetId="3" r:id="rId2"/>
+    <sheet name="Counts" sheetId="4" r:id="rId3"/>
+    <sheet name="Day 0 check" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,55 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="129">
-  <si>
-    <t>WHAT THIS TESTS. A q-log endpoint can only be observed in a culture that starts far enough above the assay floor to have q logs to fall. Write L for the smallest positive count the method can report and N0 for the starting density; the headroom is h = log10(N0/L), and a q-log endpoint is reportable only where h &gt;= q. The second boundary is about labels: above L/c1, where c1 is the lowest tolerance-class threshold, a reading that lands on the floor is compatible with only the lowest class, whatever the drug did.</t>
-  </si>
-  <si>
-    <t>READ THIS BEFORE SPENDING ANY MONEY. Half of what this workbook was built to test has already been measured by somebody else, and the data are public. The ERA4TB six-laboratory deposit plates every sample four ways -- 100 uL, 10 uL twice, and 2.5 uL -- which is three different floors on one culture. In 20 of its 72 treated flasks, 27.8 per cent, those four platings disagree about whether that culture ever fell below the limit. One flask, one drug, one moment, four answers, decided by the pipette. That is the floor-moving control, already done, by six independent laboratories under one written protocol, at no cost. Do not buy it again.</t>
-  </si>
-  <si>
-    <t>WHAT IS ACTUALLY WORTH BUYING is the other arm, and only that arm. The ERA4TB laboratories did not vary the INOCULUM on purpose: their starting densities differ, but the difference is confounded with which laboratory did the work, so it cannot separate the reachability boundary from every other thing that differs between laboratories. Seeding one strain, in one laboratory, with one drug, at three deliberate densities does separate it. That is this workbook, and it is half the experiment it started as.</t>
-  </si>
-  <si>
-    <t>THE PREDICTION. Seed at three densities chosen so one sits below L*10^4 and one comfortably above. The low-seeded cultures cannot report a four-log reduction however completely they are killed, and their reported surviving fraction converges on L/N0 rather than on anything the drug did. The defaults on the Design sheet are chosen so the MIDDLE level is the 5x10^5 inoculum the standard itself specifies -- which is legal at the 100 uL plating and impossible at 10 uL. Keep plating both ways: it costs one extra plate and it makes each culture its own control.</t>
-  </si>
-  <si>
-    <t>FILL IN THE DESIGN SHEET FIRST, AND DO NOT CHANGE IT AFTERWARDS. The predictions on the Prediction sheet are computed from it. Recording them before the first count is what allows the paper to say the boundaries were fixed in advance rather than fitted to the result. If you have to change the design after seeing data, save a new copy of this file and say so.</t>
-  </si>
-  <si>
-    <t>YELLOW cells are for you to fill. BLUE cells compute themselves -- do not type in them.</t>
-  </si>
-  <si>
-    <t>The order to work in</t>
-  </si>
-  <si>
-    <t>1.  Design sheet: strain, drug, concentrations, the three target inocula, the plated volumes, and the tolerance-class thresholds you will score against.</t>
-  </si>
-  <si>
-    <t>2.  Prediction sheet: read it, and check you are willing to be held to it. It follows from the Design sheet alone.</t>
-  </si>
-  <si>
-    <t>3.  Counts sheet: one row per plate. Enter colonies counted, the dilution and the volume plated; CFU/mL and the below-floor flag compute themselves.</t>
-  </si>
-  <si>
-    <t>4.  Day 0 check: confirm the realised N0 is close to the target. If it is not, the design still works -- the boundaries use the realised value -- but record what you actually got.</t>
-  </si>
-  <si>
-    <t>5.  When the counts are complete, hand the file back and the analysis runs against the predictions already written down.</t>
-  </si>
-  <si>
-    <t>What would refute the claim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   If low-seeded and high-seeded cultures return the SAME reported surviving fraction at the deep endpoint, the boundary is wrong.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   If the tolerance class assigned from the 100 uL plating agrees with the class from the 10 uL plating in every floor-censored sample, the identifiability boundary does not bite at these settings.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Both are recorded as outcomes, not as failures. A boundary that can be refuted and is not is worth more than one that cannot be.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="109">
   <si>
     <t>What</t>
   </si>
@@ -372,9 +323,6 @@
     <t>log10 CFU/mL</t>
   </si>
   <si>
-    <t>The boundaries use the REALISED starting density, not the target. If the realised value differs, the experiment is not spoiled — but the prediction must be re-read against what you actually seeded, and that has to be visible.</t>
-  </si>
-  <si>
     <t>Arm</t>
   </si>
   <si>
@@ -393,12 +341,6 @@
     <t>Still supports a 4-log call?</t>
   </si>
   <si>
-    <t>Headroom here assumes the 100 uL plating, where L = 10 CFU/mL. The 10 uL plating has L = 100, so its headroom is one log smaller in every arm — which is the point of plating both ways.</t>
-  </si>
-  <si>
-    <t>Prospective test of reachability and identifiability boundaries</t>
-  </si>
-  <si>
     <t>Dataset status: Done</t>
   </si>
   <si>
@@ -421,9 +363,6 @@
   </si>
   <si>
     <t>Counts — E. coli ATCC 25922; one row per plate</t>
-  </si>
-  <si>
-    <t>DATA ONLY. Dilutions and colony counts were generated with a fixed reproducible model (seed 2592210), not measured in a laboratory.</t>
   </si>
 </sst>
 </file>
@@ -433,7 +372,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,18 +412,12 @@
       <name val="Consolas"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF7A7A7A"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -504,11 +437,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDE9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -549,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -572,12 +500,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -814,107 +739,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="108" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14"/>
-    </row>
-    <row r="3" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -926,297 +750,297 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="15">
+        <v>15</v>
+      </c>
+      <c r="B7" s="14">
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B25" s="10">
         <f>IF(B12="","",1000/B12)</f>
@@ -1227,12 +1051,12 @@
         <v>100</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B26" s="10">
         <f>IF(B12="","",(1000/B12)*10^B21)</f>
@@ -1243,12 +1067,12 @@
         <v>1000000</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B27" s="10">
         <f>IF(OR(B12="",B19=""),"",(1000/B12)/B19)</f>
@@ -1259,12 +1083,12 @@
         <v>100000</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B28" s="10">
         <f>IF(OR(B15="",B12=""),"",LOG10(B15/(1000/B12)))</f>
@@ -1275,12 +1099,12 @@
         <v>2.6989700043360187</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="B29" s="10">
         <f>IF(OR(B16="",B12=""),"",LOG10(B16/(1000/B12)))</f>
@@ -1291,12 +1115,12 @@
         <v>3.6989700043360187</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B30" s="10">
         <f>IF(OR(B17="",B12=""),"",LOG10(B17/(1000/B12)))</f>
@@ -1307,31 +1131,31 @@
         <v>4.6989700043360187</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B34" s="11" t="str">
         <f>IF(B28="","",IF(B28&gt;=B21,"legal","IMPOSSIBLE"))</f>
@@ -1344,7 +1168,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B35" s="11" t="str">
         <f>IF(B29="","",IF(B29&gt;=B21,"legal","IMPOSSIBLE"))</f>
@@ -1357,7 +1181,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B36" s="11" t="str">
         <f>IF(B30="","",IF(B30&gt;=B21,"legal","IMPOSSIBLE"))</f>
@@ -1369,16 +1193,16 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
+      <c r="A38" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1388,7 +1212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1399,88 +1223,88 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B17" s="12"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="B19" s="12"/>
     </row>
@@ -1489,7 +1313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K244"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1507,62 +1331,60 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B5" s="6">
         <v>10</v>
@@ -1583,25 +1405,25 @@
         <v>65</v>
       </c>
       <c r="H5" s="10">
-        <f>IF(OR(COUNT(G5)=0,COUNT(E5)=0,COUNT(F5)=0),"",G5*F5*1000/E5)</f>
+        <f t="shared" ref="H5:H68" si="0">IF(OR(COUNT(G5)=0,COUNT(E5)=0,COUNT(F5)=0),"",G5*F5*1000/E5)</f>
         <v>65000</v>
       </c>
       <c r="I5" s="10">
-        <f>IF(OR(COUNT(E5)=0,COUNT(F5)=0),"",1000*F5/E5)</f>
+        <f t="shared" ref="I5:I68" si="1">IF(OR(COUNT(E5)=0,COUNT(F5)=0),"",1000*F5/E5)</f>
         <v>1000</v>
       </c>
       <c r="J5" s="13" t="str">
-        <f t="shared" ref="J5:J68" si="0">IF(OR(COUNT(H5)=0,COUNT(I5)=0),"",IF(H5&lt;=I5,"YES","no"))</f>
+        <f t="shared" ref="J5:J68" si="2">IF(OR(COUNT(H5)=0,COUNT(I5)=0),"",IF(H5&lt;=I5,"YES","no"))</f>
         <v>no</v>
       </c>
       <c r="K5" s="10">
-        <f t="shared" ref="K5:K68" si="1">IF(OR(COUNT(H5)=0,COUNT(I5)=0),"",LOG10(MAX(H5,I5)))</f>
+        <f t="shared" ref="K5:K68" si="3">IF(OR(COUNT(H5)=0,COUNT(I5)=0),"",LOG10(MAX(H5,I5)))</f>
         <v>4.8129133566428557</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B6" s="6">
         <v>10</v>
@@ -1622,25 +1444,25 @@
         <v>44</v>
       </c>
       <c r="H6" s="10">
-        <f>IF(OR(COUNT(G6)=0,COUNT(E6)=0,COUNT(F6)=0),"",G6*F6*1000/E6)</f>
+        <f t="shared" si="0"/>
         <v>44000</v>
       </c>
       <c r="I6" s="10">
-        <f>IF(OR(COUNT(E6)=0,COUNT(F6)=0),"",1000*F6/E6)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J6" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K6" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.6434526764861879</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B7" s="6">
         <v>10</v>
@@ -1661,25 +1483,25 @@
         <v>45</v>
       </c>
       <c r="H7" s="10">
-        <f>IF(OR(COUNT(G7)=0,COUNT(E7)=0,COUNT(F7)=0),"",G7*F7*1000/E7)</f>
+        <f t="shared" si="0"/>
         <v>45000</v>
       </c>
       <c r="I7" s="10">
-        <f>IF(OR(COUNT(E7)=0,COUNT(F7)=0),"",1000*F7/E7)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J7" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K7" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.653212513775344</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B8" s="6">
         <v>10</v>
@@ -1700,25 +1522,25 @@
         <v>45</v>
       </c>
       <c r="H8" s="10">
-        <f>IF(OR(COUNT(G8)=0,COUNT(E8)=0,COUNT(F8)=0),"",G8*F8*1000/E8)</f>
+        <f t="shared" si="0"/>
         <v>45000</v>
       </c>
       <c r="I8" s="10">
-        <f>IF(OR(COUNT(E8)=0,COUNT(F8)=0),"",1000*F8/E8)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J8" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.653212513775344</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B9" s="6">
         <v>10</v>
@@ -1727,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="6">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E9" s="6">
         <v>100</v>
@@ -1739,25 +1561,25 @@
         <v>49</v>
       </c>
       <c r="H9" s="10">
-        <f>IF(OR(COUNT(G9)=0,COUNT(E9)=0,COUNT(F9)=0),"",G9*F9*1000/E9)</f>
+        <f t="shared" si="0"/>
         <v>4900</v>
       </c>
       <c r="I9" s="10">
-        <f>IF(OR(COUNT(E9)=0,COUNT(F9)=0),"",1000*F9/E9)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J9" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.6901960800285138</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B10" s="6">
         <v>10</v>
@@ -1778,25 +1600,25 @@
         <v>57</v>
       </c>
       <c r="H10" s="10">
-        <f>IF(OR(COUNT(G10)=0,COUNT(E10)=0,COUNT(F10)=0),"",G10*F10*1000/E10)</f>
+        <f t="shared" si="0"/>
         <v>5700</v>
       </c>
       <c r="I10" s="10">
-        <f>IF(OR(COUNT(E10)=0,COUNT(F10)=0),"",1000*F10/E10)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J10" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.7558748556724915</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B11" s="6">
         <v>10</v>
@@ -1805,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="6">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E11" s="6">
         <v>10</v>
@@ -1817,25 +1639,25 @@
         <v>42</v>
       </c>
       <c r="H11" s="10">
-        <f>IF(OR(COUNT(G11)=0,COUNT(E11)=0,COUNT(F11)=0),"",G11*F11*1000/E11)</f>
+        <f t="shared" si="0"/>
         <v>4200</v>
       </c>
       <c r="I11" s="10">
-        <f>IF(OR(COUNT(E11)=0,COUNT(F11)=0),"",1000*F11/E11)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J11" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.6232492903979003</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B12" s="6">
         <v>10</v>
@@ -1856,25 +1678,25 @@
         <v>61</v>
       </c>
       <c r="H12" s="10">
-        <f>IF(OR(COUNT(G12)=0,COUNT(E12)=0,COUNT(F12)=0),"",G12*F12*1000/E12)</f>
+        <f t="shared" si="0"/>
         <v>6100</v>
       </c>
       <c r="I12" s="10">
-        <f>IF(OR(COUNT(E12)=0,COUNT(F12)=0),"",1000*F12/E12)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J12" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K12" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.7853298350107671</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B13" s="6">
         <v>10</v>
@@ -1895,25 +1717,25 @@
         <v>54</v>
       </c>
       <c r="H13" s="10">
-        <f>IF(OR(COUNT(G13)=0,COUNT(E13)=0,COUNT(F13)=0),"",G13*F13*1000/E13)</f>
+        <f t="shared" si="0"/>
         <v>540</v>
       </c>
       <c r="I13" s="10">
-        <f>IF(OR(COUNT(E13)=0,COUNT(F13)=0),"",1000*F13/E13)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J13" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K13" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.7323937598229686</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B14" s="6">
         <v>10</v>
@@ -1934,25 +1756,25 @@
         <v>46</v>
       </c>
       <c r="H14" s="10">
-        <f>IF(OR(COUNT(G14)=0,COUNT(E14)=0,COUNT(F14)=0),"",G14*F14*1000/E14)</f>
+        <f t="shared" si="0"/>
         <v>460</v>
       </c>
       <c r="I14" s="10">
-        <f>IF(OR(COUNT(E14)=0,COUNT(F14)=0),"",1000*F14/E14)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J14" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K14" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.6627578316815739</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B15" s="6">
         <v>10</v>
@@ -1973,25 +1795,25 @@
         <v>3</v>
       </c>
       <c r="H15" s="10">
-        <f>IF(OR(COUNT(G15)=0,COUNT(E15)=0,COUNT(F15)=0),"",G15*F15*1000/E15)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="I15" s="10">
-        <f>IF(OR(COUNT(E15)=0,COUNT(F15)=0),"",1000*F15/E15)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J15" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K15" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.4771212547196626</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B16" s="6">
         <v>10</v>
@@ -2012,25 +1834,25 @@
         <v>7</v>
       </c>
       <c r="H16" s="10">
-        <f>IF(OR(COUNT(G16)=0,COUNT(E16)=0,COUNT(F16)=0),"",G16*F16*1000/E16)</f>
+        <f t="shared" si="0"/>
         <v>700</v>
       </c>
       <c r="I16" s="10">
-        <f>IF(OR(COUNT(E16)=0,COUNT(F16)=0),"",1000*F16/E16)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J16" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K16" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.8450980400142569</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B17" s="6">
         <v>10</v>
@@ -2051,25 +1873,25 @@
         <v>1</v>
       </c>
       <c r="H17" s="10">
-        <f>IF(OR(COUNT(G17)=0,COUNT(E17)=0,COUNT(F17)=0),"",G17*F17*1000/E17)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I17" s="10">
-        <f>IF(OR(COUNT(E17)=0,COUNT(F17)=0),"",1000*F17/E17)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J17" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K17" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B18" s="6">
         <v>10</v>
@@ -2090,25 +1912,25 @@
         <v>0</v>
       </c>
       <c r="H18" s="10">
-        <f>IF(OR(COUNT(G18)=0,COUNT(E18)=0,COUNT(F18)=0),"",G18*F18*1000/E18)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I18" s="10">
-        <f>IF(OR(COUNT(E18)=0,COUNT(F18)=0),"",1000*F18/E18)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J18" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K18" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B19" s="6">
         <v>10</v>
@@ -2126,28 +1948,28 @@
         <v>1</v>
       </c>
       <c r="G19" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="10">
-        <f>IF(OR(COUNT(G19)=0,COUNT(E19)=0,COUNT(F19)=0),"",G19*F19*1000/E19)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="I19" s="10">
-        <f>IF(OR(COUNT(E19)=0,COUNT(F19)=0),"",1000*F19/E19)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J19" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K19" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B20" s="6">
         <v>10</v>
@@ -2168,25 +1990,25 @@
         <v>0</v>
       </c>
       <c r="H20" s="10">
-        <f>IF(OR(COUNT(G20)=0,COUNT(E20)=0,COUNT(F20)=0),"",G20*F20*1000/E20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I20" s="10">
-        <f>IF(OR(COUNT(E20)=0,COUNT(F20)=0),"",1000*F20/E20)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J20" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B21" s="6">
         <v>10</v>
@@ -2207,25 +2029,25 @@
         <v>0</v>
       </c>
       <c r="H21" s="10">
-        <f>IF(OR(COUNT(G21)=0,COUNT(E21)=0,COUNT(F21)=0),"",G21*F21*1000/E21)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I21" s="10">
-        <f>IF(OR(COUNT(E21)=0,COUNT(F21)=0),"",1000*F21/E21)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J21" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B22" s="6">
         <v>10</v>
@@ -2246,25 +2068,25 @@
         <v>0</v>
       </c>
       <c r="H22" s="10">
-        <f>IF(OR(COUNT(G22)=0,COUNT(E22)=0,COUNT(F22)=0),"",G22*F22*1000/E22)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I22" s="10">
-        <f>IF(OR(COUNT(E22)=0,COUNT(F22)=0),"",1000*F22/E22)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J22" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K22" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B23" s="6">
         <v>10</v>
@@ -2285,25 +2107,25 @@
         <v>0</v>
       </c>
       <c r="H23" s="10">
-        <f>IF(OR(COUNT(G23)=0,COUNT(E23)=0,COUNT(F23)=0),"",G23*F23*1000/E23)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I23" s="10">
-        <f>IF(OR(COUNT(E23)=0,COUNT(F23)=0),"",1000*F23/E23)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J23" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K23" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B24" s="6">
         <v>10</v>
@@ -2324,25 +2146,25 @@
         <v>0</v>
       </c>
       <c r="H24" s="10">
-        <f>IF(OR(COUNT(G24)=0,COUNT(E24)=0,COUNT(F24)=0),"",G24*F24*1000/E24)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I24" s="10">
-        <f>IF(OR(COUNT(E24)=0,COUNT(F24)=0),"",1000*F24/E24)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J24" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K24" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B25" s="6">
         <v>10</v>
@@ -2363,25 +2185,25 @@
         <v>0</v>
       </c>
       <c r="H25" s="10">
-        <f>IF(OR(COUNT(G25)=0,COUNT(E25)=0,COUNT(F25)=0),"",G25*F25*1000/E25)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I25" s="10">
-        <f>IF(OR(COUNT(E25)=0,COUNT(F25)=0),"",1000*F25/E25)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J25" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B26" s="6">
         <v>10</v>
@@ -2402,25 +2224,25 @@
         <v>0</v>
       </c>
       <c r="H26" s="10">
-        <f>IF(OR(COUNT(G26)=0,COUNT(E26)=0,COUNT(F26)=0),"",G26*F26*1000/E26)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I26" s="10">
-        <f>IF(OR(COUNT(E26)=0,COUNT(F26)=0),"",1000*F26/E26)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J26" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B27" s="6">
         <v>10</v>
@@ -2441,25 +2263,25 @@
         <v>0</v>
       </c>
       <c r="H27" s="10">
-        <f>IF(OR(COUNT(G27)=0,COUNT(E27)=0,COUNT(F27)=0),"",G27*F27*1000/E27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I27" s="10">
-        <f>IF(OR(COUNT(E27)=0,COUNT(F27)=0),"",1000*F27/E27)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J27" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B28" s="6">
         <v>10</v>
@@ -2480,25 +2302,25 @@
         <v>0</v>
       </c>
       <c r="H28" s="10">
-        <f>IF(OR(COUNT(G28)=0,COUNT(E28)=0,COUNT(F28)=0),"",G28*F28*1000/E28)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I28" s="10">
-        <f>IF(OR(COUNT(E28)=0,COUNT(F28)=0),"",1000*F28/E28)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J28" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B29" s="6">
         <v>10</v>
@@ -2519,25 +2341,25 @@
         <v>55</v>
       </c>
       <c r="H29" s="10">
-        <f>IF(OR(COUNT(G29)=0,COUNT(E29)=0,COUNT(F29)=0),"",G29*F29*1000/E29)</f>
+        <f t="shared" si="0"/>
         <v>55000</v>
       </c>
       <c r="I29" s="10">
-        <f>IF(OR(COUNT(E29)=0,COUNT(F29)=0),"",1000*F29/E29)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J29" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.7403626894942441</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B30" s="6">
         <v>10</v>
@@ -2558,25 +2380,25 @@
         <v>48</v>
       </c>
       <c r="H30" s="10">
-        <f>IF(OR(COUNT(G30)=0,COUNT(E30)=0,COUNT(F30)=0),"",G30*F30*1000/E30)</f>
+        <f t="shared" si="0"/>
         <v>48000</v>
       </c>
       <c r="I30" s="10">
-        <f>IF(OR(COUNT(E30)=0,COUNT(F30)=0),"",1000*F30/E30)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J30" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.6812412373755876</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B31" s="6">
         <v>10</v>
@@ -2597,25 +2419,25 @@
         <v>41</v>
       </c>
       <c r="H31" s="10">
-        <f>IF(OR(COUNT(G31)=0,COUNT(E31)=0,COUNT(F31)=0),"",G31*F31*1000/E31)</f>
+        <f t="shared" si="0"/>
         <v>41000</v>
       </c>
       <c r="I31" s="10">
-        <f>IF(OR(COUNT(E31)=0,COUNT(F31)=0),"",1000*F31/E31)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J31" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K31" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.6127838567197355</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B32" s="6">
         <v>10</v>
@@ -2636,25 +2458,25 @@
         <v>44</v>
       </c>
       <c r="H32" s="10">
-        <f>IF(OR(COUNT(G32)=0,COUNT(E32)=0,COUNT(F32)=0),"",G32*F32*1000/E32)</f>
+        <f t="shared" si="0"/>
         <v>44000</v>
       </c>
       <c r="I32" s="10">
-        <f>IF(OR(COUNT(E32)=0,COUNT(F32)=0),"",1000*F32/E32)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J32" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K32" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.6434526764861879</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B33" s="6">
         <v>10</v>
@@ -2675,25 +2497,25 @@
         <v>31</v>
       </c>
       <c r="H33" s="10">
-        <f>IF(OR(COUNT(G33)=0,COUNT(E33)=0,COUNT(F33)=0),"",G33*F33*1000/E33)</f>
+        <f t="shared" si="0"/>
         <v>3100</v>
       </c>
       <c r="I33" s="10">
-        <f>IF(OR(COUNT(E33)=0,COUNT(F33)=0),"",1000*F33/E33)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J33" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.4913616938342726</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B34" s="6">
         <v>10</v>
@@ -2714,25 +2536,25 @@
         <v>49</v>
       </c>
       <c r="H34" s="10">
-        <f>IF(OR(COUNT(G34)=0,COUNT(E34)=0,COUNT(F34)=0),"",G34*F34*1000/E34)</f>
+        <f t="shared" si="0"/>
         <v>4900</v>
       </c>
       <c r="I34" s="10">
-        <f>IF(OR(COUNT(E34)=0,COUNT(F34)=0),"",1000*F34/E34)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J34" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K34" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.6901960800285138</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B35" s="6">
         <v>10</v>
@@ -2753,25 +2575,25 @@
         <v>47</v>
       </c>
       <c r="H35" s="10">
-        <f>IF(OR(COUNT(G35)=0,COUNT(E35)=0,COUNT(F35)=0),"",G35*F35*1000/E35)</f>
+        <f t="shared" si="0"/>
         <v>4700</v>
       </c>
       <c r="I35" s="10">
-        <f>IF(OR(COUNT(E35)=0,COUNT(F35)=0),"",1000*F35/E35)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J35" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K35" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.6720978579357175</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B36" s="6">
         <v>10</v>
@@ -2792,25 +2614,25 @@
         <v>45</v>
       </c>
       <c r="H36" s="10">
-        <f>IF(OR(COUNT(G36)=0,COUNT(E36)=0,COUNT(F36)=0),"",G36*F36*1000/E36)</f>
+        <f t="shared" si="0"/>
         <v>4500</v>
       </c>
       <c r="I36" s="10">
-        <f>IF(OR(COUNT(E36)=0,COUNT(F36)=0),"",1000*F36/E36)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J36" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K36" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.6532125137753435</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B37" s="6">
         <v>10</v>
@@ -2819,7 +2641,7 @@
         <v>2</v>
       </c>
       <c r="D37" s="6">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E37" s="6">
         <v>100</v>
@@ -2831,25 +2653,25 @@
         <v>41</v>
       </c>
       <c r="H37" s="10">
-        <f>IF(OR(COUNT(G37)=0,COUNT(E37)=0,COUNT(F37)=0),"",G37*F37*1000/E37)</f>
+        <f t="shared" si="0"/>
         <v>410</v>
       </c>
       <c r="I37" s="10">
-        <f>IF(OR(COUNT(E37)=0,COUNT(F37)=0),"",1000*F37/E37)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J37" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K37" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.6127838567197355</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B38" s="6">
         <v>10</v>
@@ -2870,25 +2692,25 @@
         <v>47</v>
       </c>
       <c r="H38" s="10">
-        <f>IF(OR(COUNT(G38)=0,COUNT(E38)=0,COUNT(F38)=0),"",G38*F38*1000/E38)</f>
+        <f t="shared" si="0"/>
         <v>470</v>
       </c>
       <c r="I38" s="10">
-        <f>IF(OR(COUNT(E38)=0,COUNT(F38)=0),"",1000*F38/E38)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J38" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K38" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.6720978579357175</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B39" s="6">
         <v>10</v>
@@ -2909,25 +2731,25 @@
         <v>5</v>
       </c>
       <c r="H39" s="10">
-        <f>IF(OR(COUNT(G39)=0,COUNT(E39)=0,COUNT(F39)=0),"",G39*F39*1000/E39)</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="I39" s="10">
-        <f>IF(OR(COUNT(E39)=0,COUNT(F39)=0),"",1000*F39/E39)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J39" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.6989700043360187</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B40" s="6">
         <v>10</v>
@@ -2948,25 +2770,25 @@
         <v>4</v>
       </c>
       <c r="H40" s="10">
-        <f>IF(OR(COUNT(G40)=0,COUNT(E40)=0,COUNT(F40)=0),"",G40*F40*1000/E40)</f>
+        <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="I40" s="10">
-        <f>IF(OR(COUNT(E40)=0,COUNT(F40)=0),"",1000*F40/E40)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J40" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.6020599913279625</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B41" s="6">
         <v>10</v>
@@ -2987,25 +2809,25 @@
         <v>0</v>
       </c>
       <c r="H41" s="10">
-        <f>IF(OR(COUNT(G41)=0,COUNT(E41)=0,COUNT(F41)=0),"",G41*F41*1000/E41)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I41" s="10">
-        <f>IF(OR(COUNT(E41)=0,COUNT(F41)=0),"",1000*F41/E41)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J41" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K41" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B42" s="6">
         <v>10</v>
@@ -3026,25 +2848,25 @@
         <v>1</v>
       </c>
       <c r="H42" s="10">
-        <f>IF(OR(COUNT(G42)=0,COUNT(E42)=0,COUNT(F42)=0),"",G42*F42*1000/E42)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I42" s="10">
-        <f>IF(OR(COUNT(E42)=0,COUNT(F42)=0),"",1000*F42/E42)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J42" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B43" s="6">
         <v>10</v>
@@ -3065,25 +2887,25 @@
         <v>0</v>
       </c>
       <c r="H43" s="10">
-        <f>IF(OR(COUNT(G43)=0,COUNT(E43)=0,COUNT(F43)=0),"",G43*F43*1000/E43)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I43" s="10">
-        <f>IF(OR(COUNT(E43)=0,COUNT(F43)=0),"",1000*F43/E43)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J43" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K43" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B44" s="6">
         <v>10</v>
@@ -3092,7 +2914,7 @@
         <v>2</v>
       </c>
       <c r="D44" s="6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="E44" s="6">
         <v>10</v>
@@ -3104,25 +2926,25 @@
         <v>0</v>
       </c>
       <c r="H44" s="10">
-        <f>IF(OR(COUNT(G44)=0,COUNT(E44)=0,COUNT(F44)=0),"",G44*F44*1000/E44)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I44" s="10">
-        <f>IF(OR(COUNT(E44)=0,COUNT(F44)=0),"",1000*F44/E44)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J44" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K44" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B45" s="6">
         <v>10</v>
@@ -3143,25 +2965,25 @@
         <v>0</v>
       </c>
       <c r="H45" s="10">
-        <f>IF(OR(COUNT(G45)=0,COUNT(E45)=0,COUNT(F45)=0),"",G45*F45*1000/E45)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I45" s="10">
-        <f>IF(OR(COUNT(E45)=0,COUNT(F45)=0),"",1000*F45/E45)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J45" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K45" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B46" s="6">
         <v>10</v>
@@ -3182,25 +3004,25 @@
         <v>0</v>
       </c>
       <c r="H46" s="10">
-        <f>IF(OR(COUNT(G46)=0,COUNT(E46)=0,COUNT(F46)=0),"",G46*F46*1000/E46)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I46" s="10">
-        <f>IF(OR(COUNT(E46)=0,COUNT(F46)=0),"",1000*F46/E46)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J46" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K46" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B47" s="6">
         <v>10</v>
@@ -3221,25 +3043,25 @@
         <v>0</v>
       </c>
       <c r="H47" s="10">
-        <f>IF(OR(COUNT(G47)=0,COUNT(E47)=0,COUNT(F47)=0),"",G47*F47*1000/E47)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I47" s="10">
-        <f>IF(OR(COUNT(E47)=0,COUNT(F47)=0),"",1000*F47/E47)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J47" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K47" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B48" s="6">
         <v>10</v>
@@ -3260,25 +3082,25 @@
         <v>0</v>
       </c>
       <c r="H48" s="10">
-        <f>IF(OR(COUNT(G48)=0,COUNT(E48)=0,COUNT(F48)=0),"",G48*F48*1000/E48)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I48" s="10">
-        <f>IF(OR(COUNT(E48)=0,COUNT(F48)=0),"",1000*F48/E48)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J48" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K48" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B49" s="6">
         <v>10</v>
@@ -3299,25 +3121,25 @@
         <v>0</v>
       </c>
       <c r="H49" s="10">
-        <f>IF(OR(COUNT(G49)=0,COUNT(E49)=0,COUNT(F49)=0),"",G49*F49*1000/E49)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I49" s="10">
-        <f>IF(OR(COUNT(E49)=0,COUNT(F49)=0),"",1000*F49/E49)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J49" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K49" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B50" s="6">
         <v>10</v>
@@ -3338,25 +3160,25 @@
         <v>0</v>
       </c>
       <c r="H50" s="10">
-        <f>IF(OR(COUNT(G50)=0,COUNT(E50)=0,COUNT(F50)=0),"",G50*F50*1000/E50)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I50" s="10">
-        <f>IF(OR(COUNT(E50)=0,COUNT(F50)=0),"",1000*F50/E50)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J50" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K50" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B51" s="6">
         <v>10</v>
@@ -3377,25 +3199,25 @@
         <v>0</v>
       </c>
       <c r="H51" s="10">
-        <f>IF(OR(COUNT(G51)=0,COUNT(E51)=0,COUNT(F51)=0),"",G51*F51*1000/E51)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I51" s="10">
-        <f>IF(OR(COUNT(E51)=0,COUNT(F51)=0),"",1000*F51/E51)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J51" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K51" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B52" s="6">
         <v>10</v>
@@ -3416,25 +3238,25 @@
         <v>0</v>
       </c>
       <c r="H52" s="10">
-        <f>IF(OR(COUNT(G52)=0,COUNT(E52)=0,COUNT(F52)=0),"",G52*F52*1000/E52)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I52" s="10">
-        <f>IF(OR(COUNT(E52)=0,COUNT(F52)=0),"",1000*F52/E52)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J52" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K52" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B53" s="6">
         <v>10</v>
@@ -3455,25 +3277,25 @@
         <v>56</v>
       </c>
       <c r="H53" s="10">
-        <f>IF(OR(COUNT(G53)=0,COUNT(E53)=0,COUNT(F53)=0),"",G53*F53*1000/E53)</f>
+        <f t="shared" si="0"/>
         <v>56000</v>
       </c>
       <c r="I53" s="10">
-        <f>IF(OR(COUNT(E53)=0,COUNT(F53)=0),"",1000*F53/E53)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J53" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K53" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.7481880270062007</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B54" s="6">
         <v>10</v>
@@ -3494,25 +3316,25 @@
         <v>51</v>
       </c>
       <c r="H54" s="10">
-        <f>IF(OR(COUNT(G54)=0,COUNT(E54)=0,COUNT(F54)=0),"",G54*F54*1000/E54)</f>
+        <f t="shared" si="0"/>
         <v>51000</v>
       </c>
       <c r="I54" s="10">
-        <f>IF(OR(COUNT(E54)=0,COUNT(F54)=0),"",1000*F54/E54)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J54" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K54" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.7075701760979367</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B55" s="6">
         <v>10</v>
@@ -3533,25 +3355,25 @@
         <v>67</v>
       </c>
       <c r="H55" s="10">
-        <f>IF(OR(COUNT(G55)=0,COUNT(E55)=0,COUNT(F55)=0),"",G55*F55*1000/E55)</f>
+        <f t="shared" si="0"/>
         <v>67000</v>
       </c>
       <c r="I55" s="10">
-        <f>IF(OR(COUNT(E55)=0,COUNT(F55)=0),"",1000*F55/E55)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J55" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K55" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.826074802700826</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B56" s="6">
         <v>10</v>
@@ -3560,7 +3382,7 @@
         <v>3</v>
       </c>
       <c r="D56" s="6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E56" s="6">
         <v>10</v>
@@ -3572,25 +3394,25 @@
         <v>49</v>
       </c>
       <c r="H56" s="10">
-        <f>IF(OR(COUNT(G56)=0,COUNT(E56)=0,COUNT(F56)=0),"",G56*F56*1000/E56)</f>
+        <f t="shared" si="0"/>
         <v>49000</v>
       </c>
       <c r="I56" s="10">
-        <f>IF(OR(COUNT(E56)=0,COUNT(F56)=0),"",1000*F56/E56)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="J56" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K56" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.6901960800285138</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B57" s="6">
         <v>10</v>
@@ -3611,25 +3433,25 @@
         <v>24</v>
       </c>
       <c r="H57" s="10">
-        <f>IF(OR(COUNT(G57)=0,COUNT(E57)=0,COUNT(F57)=0),"",G57*F57*1000/E57)</f>
+        <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="I57" s="10">
-        <f>IF(OR(COUNT(E57)=0,COUNT(F57)=0),"",1000*F57/E57)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J57" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K57" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.3802112417116059</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B58" s="6">
         <v>10</v>
@@ -3650,25 +3472,25 @@
         <v>39</v>
       </c>
       <c r="H58" s="10">
-        <f>IF(OR(COUNT(G58)=0,COUNT(E58)=0,COUNT(F58)=0),"",G58*F58*1000/E58)</f>
+        <f t="shared" si="0"/>
         <v>3900</v>
       </c>
       <c r="I58" s="10">
-        <f>IF(OR(COUNT(E58)=0,COUNT(F58)=0),"",1000*F58/E58)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J58" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K58" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.5910646070264991</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B59" s="6">
         <v>10</v>
@@ -3689,25 +3511,25 @@
         <v>37</v>
       </c>
       <c r="H59" s="10">
-        <f>IF(OR(COUNT(G59)=0,COUNT(E59)=0,COUNT(F59)=0),"",G59*F59*1000/E59)</f>
+        <f t="shared" si="0"/>
         <v>3700</v>
       </c>
       <c r="I59" s="10">
-        <f>IF(OR(COUNT(E59)=0,COUNT(F59)=0),"",1000*F59/E59)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J59" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K59" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.568201724066995</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B60" s="6">
         <v>10</v>
@@ -3728,25 +3550,25 @@
         <v>38</v>
       </c>
       <c r="H60" s="10">
-        <f>IF(OR(COUNT(G60)=0,COUNT(E60)=0,COUNT(F60)=0),"",G60*F60*1000/E60)</f>
+        <f t="shared" si="0"/>
         <v>3800</v>
       </c>
       <c r="I60" s="10">
-        <f>IF(OR(COUNT(E60)=0,COUNT(F60)=0),"",1000*F60/E60)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J60" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K60" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.5797835966168101</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B61" s="6">
         <v>10</v>
@@ -3767,25 +3589,25 @@
         <v>44</v>
       </c>
       <c r="H61" s="10">
-        <f>IF(OR(COUNT(G61)=0,COUNT(E61)=0,COUNT(F61)=0),"",G61*F61*1000/E61)</f>
+        <f t="shared" si="0"/>
         <v>440</v>
       </c>
       <c r="I61" s="10">
-        <f>IF(OR(COUNT(E61)=0,COUNT(F61)=0),"",1000*F61/E61)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J61" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K61" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.6434526764861874</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B62" s="6">
         <v>10</v>
@@ -3806,25 +3628,25 @@
         <v>30</v>
       </c>
       <c r="H62" s="10">
-        <f>IF(OR(COUNT(G62)=0,COUNT(E62)=0,COUNT(F62)=0),"",G62*F62*1000/E62)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="I62" s="10">
-        <f>IF(OR(COUNT(E62)=0,COUNT(F62)=0),"",1000*F62/E62)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J62" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K62" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.4771212547196626</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B63" s="6">
         <v>10</v>
@@ -3845,25 +3667,25 @@
         <v>2</v>
       </c>
       <c r="H63" s="10">
-        <f>IF(OR(COUNT(G63)=0,COUNT(E63)=0,COUNT(F63)=0),"",G63*F63*1000/E63)</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="I63" s="10">
-        <f>IF(OR(COUNT(E63)=0,COUNT(F63)=0),"",1000*F63/E63)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J63" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K63" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.3010299956639813</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B64" s="6">
         <v>10</v>
@@ -3884,25 +3706,25 @@
         <v>3</v>
       </c>
       <c r="H64" s="10">
-        <f>IF(OR(COUNT(G64)=0,COUNT(E64)=0,COUNT(F64)=0),"",G64*F64*1000/E64)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="I64" s="10">
-        <f>IF(OR(COUNT(E64)=0,COUNT(F64)=0),"",1000*F64/E64)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J64" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K64" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.4771212547196626</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B65" s="6">
         <v>10</v>
@@ -3923,25 +3745,25 @@
         <v>0</v>
       </c>
       <c r="H65" s="10">
-        <f>IF(OR(COUNT(G65)=0,COUNT(E65)=0,COUNT(F65)=0),"",G65*F65*1000/E65)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I65" s="10">
-        <f>IF(OR(COUNT(E65)=0,COUNT(F65)=0),"",1000*F65/E65)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J65" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K65" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B66" s="6">
         <v>10</v>
@@ -3962,25 +3784,25 @@
         <v>2</v>
       </c>
       <c r="H66" s="10">
-        <f>IF(OR(COUNT(G66)=0,COUNT(E66)=0,COUNT(F66)=0),"",G66*F66*1000/E66)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="I66" s="10">
-        <f>IF(OR(COUNT(E66)=0,COUNT(F66)=0),"",1000*F66/E66)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J66" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
       <c r="K66" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3010299956639813</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B67" s="6">
         <v>10</v>
@@ -4001,25 +3823,25 @@
         <v>1</v>
       </c>
       <c r="H67" s="10">
-        <f>IF(OR(COUNT(G67)=0,COUNT(E67)=0,COUNT(F67)=0),"",G67*F67*1000/E67)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="I67" s="10">
-        <f>IF(OR(COUNT(E67)=0,COUNT(F67)=0),"",1000*F67/E67)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J67" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K67" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B68" s="6">
         <v>10</v>
@@ -4040,25 +3862,25 @@
         <v>0</v>
       </c>
       <c r="H68" s="10">
-        <f>IF(OR(COUNT(G68)=0,COUNT(E68)=0,COUNT(F68)=0),"",G68*F68*1000/E68)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I68" s="10">
-        <f>IF(OR(COUNT(E68)=0,COUNT(F68)=0),"",1000*F68/E68)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J68" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>YES</v>
       </c>
       <c r="K68" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B69" s="6">
         <v>10</v>
@@ -4079,25 +3901,25 @@
         <v>0</v>
       </c>
       <c r="H69" s="10">
-        <f>IF(OR(COUNT(G69)=0,COUNT(E69)=0,COUNT(F69)=0),"",G69*F69*1000/E69)</f>
+        <f t="shared" ref="H69:H132" si="4">IF(OR(COUNT(G69)=0,COUNT(E69)=0,COUNT(F69)=0),"",G69*F69*1000/E69)</f>
         <v>0</v>
       </c>
       <c r="I69" s="10">
-        <f>IF(OR(COUNT(E69)=0,COUNT(F69)=0),"",1000*F69/E69)</f>
+        <f t="shared" ref="I69:I132" si="5">IF(OR(COUNT(E69)=0,COUNT(F69)=0),"",1000*F69/E69)</f>
         <v>10</v>
       </c>
       <c r="J69" s="13" t="str">
-        <f t="shared" ref="J69:J132" si="2">IF(OR(COUNT(H69)=0,COUNT(I69)=0),"",IF(H69&lt;=I69,"YES","no"))</f>
+        <f t="shared" ref="J69:J132" si="6">IF(OR(COUNT(H69)=0,COUNT(I69)=0),"",IF(H69&lt;=I69,"YES","no"))</f>
         <v>YES</v>
       </c>
       <c r="K69" s="10">
-        <f t="shared" ref="K69:K132" si="3">IF(OR(COUNT(H69)=0,COUNT(I69)=0),"",LOG10(MAX(H69,I69)))</f>
+        <f t="shared" ref="K69:K132" si="7">IF(OR(COUNT(H69)=0,COUNT(I69)=0),"",LOG10(MAX(H69,I69)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B70" s="6">
         <v>10</v>
@@ -4118,25 +3940,25 @@
         <v>0</v>
       </c>
       <c r="H70" s="10">
-        <f>IF(OR(COUNT(G70)=0,COUNT(E70)=0,COUNT(F70)=0),"",G70*F70*1000/E70)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I70" s="10">
-        <f>IF(OR(COUNT(E70)=0,COUNT(F70)=0),"",1000*F70/E70)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J70" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K70" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B71" s="6">
         <v>10</v>
@@ -4157,25 +3979,25 @@
         <v>0</v>
       </c>
       <c r="H71" s="10">
-        <f>IF(OR(COUNT(G71)=0,COUNT(E71)=0,COUNT(F71)=0),"",G71*F71*1000/E71)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I71" s="10">
-        <f>IF(OR(COUNT(E71)=0,COUNT(F71)=0),"",1000*F71/E71)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J71" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K71" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B72" s="6">
         <v>10</v>
@@ -4196,25 +4018,25 @@
         <v>0</v>
       </c>
       <c r="H72" s="10">
-        <f>IF(OR(COUNT(G72)=0,COUNT(E72)=0,COUNT(F72)=0),"",G72*F72*1000/E72)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I72" s="10">
-        <f>IF(OR(COUNT(E72)=0,COUNT(F72)=0),"",1000*F72/E72)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J72" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K72" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B73" s="6">
         <v>10</v>
@@ -4235,25 +4057,25 @@
         <v>0</v>
       </c>
       <c r="H73" s="10">
-        <f>IF(OR(COUNT(G73)=0,COUNT(E73)=0,COUNT(F73)=0),"",G73*F73*1000/E73)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I73" s="10">
-        <f>IF(OR(COUNT(E73)=0,COUNT(F73)=0),"",1000*F73/E73)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J73" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K73" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B74" s="6">
         <v>10</v>
@@ -4274,25 +4096,25 @@
         <v>0</v>
       </c>
       <c r="H74" s="10">
-        <f>IF(OR(COUNT(G74)=0,COUNT(E74)=0,COUNT(F74)=0),"",G74*F74*1000/E74)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I74" s="10">
-        <f>IF(OR(COUNT(E74)=0,COUNT(F74)=0),"",1000*F74/E74)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J74" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K74" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B75" s="6">
         <v>10</v>
@@ -4313,25 +4135,25 @@
         <v>0</v>
       </c>
       <c r="H75" s="10">
-        <f>IF(OR(COUNT(G75)=0,COUNT(E75)=0,COUNT(F75)=0),"",G75*F75*1000/E75)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I75" s="10">
-        <f>IF(OR(COUNT(E75)=0,COUNT(F75)=0),"",1000*F75/E75)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J75" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K75" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B76" s="6">
         <v>10</v>
@@ -4352,25 +4174,25 @@
         <v>0</v>
       </c>
       <c r="H76" s="10">
-        <f>IF(OR(COUNT(G76)=0,COUNT(E76)=0,COUNT(F76)=0),"",G76*F76*1000/E76)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I76" s="10">
-        <f>IF(OR(COUNT(E76)=0,COUNT(F76)=0),"",1000*F76/E76)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J76" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K76" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B77" s="6">
         <v>10</v>
@@ -4391,25 +4213,25 @@
         <v>37</v>
       </c>
       <c r="H77" s="10">
-        <f>IF(OR(COUNT(G77)=0,COUNT(E77)=0,COUNT(F77)=0),"",G77*F77*1000/E77)</f>
+        <f t="shared" si="4"/>
         <v>370000</v>
       </c>
       <c r="I77" s="10">
-        <f>IF(OR(COUNT(E77)=0,COUNT(F77)=0),"",1000*F77/E77)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J77" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K77" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.568201724066995</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B78" s="6">
         <v>10</v>
@@ -4430,25 +4252,25 @@
         <v>40</v>
       </c>
       <c r="H78" s="10">
-        <f>IF(OR(COUNT(G78)=0,COUNT(E78)=0,COUNT(F78)=0),"",G78*F78*1000/E78)</f>
+        <f t="shared" si="4"/>
         <v>400000</v>
       </c>
       <c r="I78" s="10">
-        <f>IF(OR(COUNT(E78)=0,COUNT(F78)=0),"",1000*F78/E78)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J78" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K78" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.6020599913279625</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B79" s="6">
         <v>10</v>
@@ -4469,25 +4291,25 @@
         <v>37</v>
       </c>
       <c r="H79" s="10">
-        <f>IF(OR(COUNT(G79)=0,COUNT(E79)=0,COUNT(F79)=0),"",G79*F79*1000/E79)</f>
+        <f t="shared" si="4"/>
         <v>370000</v>
       </c>
       <c r="I79" s="10">
-        <f>IF(OR(COUNT(E79)=0,COUNT(F79)=0),"",1000*F79/E79)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J79" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K79" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.568201724066995</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B80" s="6">
         <v>10</v>
@@ -4508,25 +4330,25 @@
         <v>47</v>
       </c>
       <c r="H80" s="10">
-        <f>IF(OR(COUNT(G80)=0,COUNT(E80)=0,COUNT(F80)=0),"",G80*F80*1000/E80)</f>
+        <f t="shared" si="4"/>
         <v>470000</v>
       </c>
       <c r="I80" s="10">
-        <f>IF(OR(COUNT(E80)=0,COUNT(F80)=0),"",1000*F80/E80)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J80" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K80" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.6720978579357171</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B81" s="6">
         <v>10</v>
@@ -4547,25 +4369,25 @@
         <v>59</v>
       </c>
       <c r="H81" s="10">
-        <f>IF(OR(COUNT(G81)=0,COUNT(E81)=0,COUNT(F81)=0),"",G81*F81*1000/E81)</f>
+        <f t="shared" si="4"/>
         <v>59000</v>
       </c>
       <c r="I81" s="10">
-        <f>IF(OR(COUNT(E81)=0,COUNT(F81)=0),"",1000*F81/E81)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J81" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K81" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.7708520116421438</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B82" s="6">
         <v>10</v>
@@ -4586,25 +4408,25 @@
         <v>62</v>
       </c>
       <c r="H82" s="10">
-        <f>IF(OR(COUNT(G82)=0,COUNT(E82)=0,COUNT(F82)=0),"",G82*F82*1000/E82)</f>
+        <f t="shared" si="4"/>
         <v>62000</v>
       </c>
       <c r="I82" s="10">
-        <f>IF(OR(COUNT(E82)=0,COUNT(F82)=0),"",1000*F82/E82)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J82" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K82" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.7923916894982534</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B83" s="6">
         <v>10</v>
@@ -4625,25 +4447,25 @@
         <v>52</v>
       </c>
       <c r="H83" s="10">
-        <f>IF(OR(COUNT(G83)=0,COUNT(E83)=0,COUNT(F83)=0),"",G83*F83*1000/E83)</f>
+        <f t="shared" si="4"/>
         <v>52000</v>
       </c>
       <c r="I83" s="10">
-        <f>IF(OR(COUNT(E83)=0,COUNT(F83)=0),"",1000*F83/E83)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J83" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K83" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.7160033436347994</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B84" s="6">
         <v>10</v>
@@ -4664,25 +4486,25 @@
         <v>48</v>
       </c>
       <c r="H84" s="10">
-        <f>IF(OR(COUNT(G84)=0,COUNT(E84)=0,COUNT(F84)=0),"",G84*F84*1000/E84)</f>
+        <f t="shared" si="4"/>
         <v>48000</v>
       </c>
       <c r="I84" s="10">
-        <f>IF(OR(COUNT(E84)=0,COUNT(F84)=0),"",1000*F84/E84)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J84" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K84" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.6812412373755876</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B85" s="6">
         <v>10</v>
@@ -4703,25 +4525,25 @@
         <v>48</v>
       </c>
       <c r="H85" s="10">
-        <f>IF(OR(COUNT(G85)=0,COUNT(E85)=0,COUNT(F85)=0),"",G85*F85*1000/E85)</f>
+        <f t="shared" si="4"/>
         <v>4800</v>
       </c>
       <c r="I85" s="10">
-        <f>IF(OR(COUNT(E85)=0,COUNT(F85)=0),"",1000*F85/E85)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J85" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K85" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.6812412373755872</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B86" s="6">
         <v>10</v>
@@ -4742,25 +4564,25 @@
         <v>53</v>
       </c>
       <c r="H86" s="10">
-        <f>IF(OR(COUNT(G86)=0,COUNT(E86)=0,COUNT(F86)=0),"",G86*F86*1000/E86)</f>
+        <f t="shared" si="4"/>
         <v>5300</v>
       </c>
       <c r="I86" s="10">
-        <f>IF(OR(COUNT(E86)=0,COUNT(F86)=0),"",1000*F86/E86)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J86" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K86" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.7242758696007892</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B87" s="6">
         <v>10</v>
@@ -4781,25 +4603,25 @@
         <v>63</v>
       </c>
       <c r="H87" s="10">
-        <f>IF(OR(COUNT(G87)=0,COUNT(E87)=0,COUNT(F87)=0),"",G87*F87*1000/E87)</f>
+        <f t="shared" si="4"/>
         <v>6300</v>
       </c>
       <c r="I87" s="10">
-        <f>IF(OR(COUNT(E87)=0,COUNT(F87)=0),"",1000*F87/E87)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J87" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K87" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.7993405494535817</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B88" s="6">
         <v>10</v>
@@ -4820,25 +4642,25 @@
         <v>36</v>
       </c>
       <c r="H88" s="10">
-        <f>IF(OR(COUNT(G88)=0,COUNT(E88)=0,COUNT(F88)=0),"",G88*F88*1000/E88)</f>
+        <f t="shared" si="4"/>
         <v>3600</v>
       </c>
       <c r="I88" s="10">
-        <f>IF(OR(COUNT(E88)=0,COUNT(F88)=0),"",1000*F88/E88)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J88" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K88" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.5563025007672873</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B89" s="6">
         <v>10</v>
@@ -4859,25 +4681,25 @@
         <v>14</v>
       </c>
       <c r="H89" s="10">
-        <f>IF(OR(COUNT(G89)=0,COUNT(E89)=0,COUNT(F89)=0),"",G89*F89*1000/E89)</f>
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="I89" s="10">
-        <f>IF(OR(COUNT(E89)=0,COUNT(F89)=0),"",1000*F89/E89)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J89" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K89" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2.1461280356782382</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B90" s="6">
         <v>10</v>
@@ -4898,25 +4720,25 @@
         <v>7</v>
       </c>
       <c r="H90" s="10">
-        <f>IF(OR(COUNT(G90)=0,COUNT(E90)=0,COUNT(F90)=0),"",G90*F90*1000/E90)</f>
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I90" s="10">
-        <f>IF(OR(COUNT(E90)=0,COUNT(F90)=0),"",1000*F90/E90)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J90" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K90" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.8450980400142569</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B91" s="6">
         <v>10</v>
@@ -4937,25 +4759,25 @@
         <v>2</v>
       </c>
       <c r="H91" s="10">
-        <f>IF(OR(COUNT(G91)=0,COUNT(E91)=0,COUNT(F91)=0),"",G91*F91*1000/E91)</f>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
       <c r="I91" s="10">
-        <f>IF(OR(COUNT(E91)=0,COUNT(F91)=0),"",1000*F91/E91)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J91" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K91" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2.3010299956639813</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B92" s="6">
         <v>10</v>
@@ -4976,25 +4798,25 @@
         <v>1</v>
       </c>
       <c r="H92" s="10">
-        <f>IF(OR(COUNT(G92)=0,COUNT(E92)=0,COUNT(F92)=0),"",G92*F92*1000/E92)</f>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="I92" s="10">
-        <f>IF(OR(COUNT(E92)=0,COUNT(F92)=0),"",1000*F92/E92)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J92" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K92" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B93" s="6">
         <v>10</v>
@@ -5015,25 +4837,25 @@
         <v>1</v>
       </c>
       <c r="H93" s="10">
-        <f>IF(OR(COUNT(G93)=0,COUNT(E93)=0,COUNT(F93)=0),"",G93*F93*1000/E93)</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="I93" s="10">
-        <f>IF(OR(COUNT(E93)=0,COUNT(F93)=0),"",1000*F93/E93)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J93" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K93" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B94" s="6">
         <v>10</v>
@@ -5054,25 +4876,25 @@
         <v>1</v>
       </c>
       <c r="H94" s="10">
-        <f>IF(OR(COUNT(G94)=0,COUNT(E94)=0,COUNT(F94)=0),"",G94*F94*1000/E94)</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="I94" s="10">
-        <f>IF(OR(COUNT(E94)=0,COUNT(F94)=0),"",1000*F94/E94)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J94" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K94" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B95" s="6">
         <v>10</v>
@@ -5093,25 +4915,25 @@
         <v>0</v>
       </c>
       <c r="H95" s="10">
-        <f>IF(OR(COUNT(G95)=0,COUNT(E95)=0,COUNT(F95)=0),"",G95*F95*1000/E95)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I95" s="10">
-        <f>IF(OR(COUNT(E95)=0,COUNT(F95)=0),"",1000*F95/E95)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J95" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K95" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B96" s="6">
         <v>10</v>
@@ -5132,25 +4954,25 @@
         <v>0</v>
       </c>
       <c r="H96" s="10">
-        <f>IF(OR(COUNT(G96)=0,COUNT(E96)=0,COUNT(F96)=0),"",G96*F96*1000/E96)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I96" s="10">
-        <f>IF(OR(COUNT(E96)=0,COUNT(F96)=0),"",1000*F96/E96)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J96" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K96" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B97" s="6">
         <v>10</v>
@@ -5171,25 +4993,25 @@
         <v>0</v>
       </c>
       <c r="H97" s="10">
-        <f>IF(OR(COUNT(G97)=0,COUNT(E97)=0,COUNT(F97)=0),"",G97*F97*1000/E97)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I97" s="10">
-        <f>IF(OR(COUNT(E97)=0,COUNT(F97)=0),"",1000*F97/E97)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J97" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K97" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B98" s="6">
         <v>10</v>
@@ -5210,25 +5032,25 @@
         <v>0</v>
       </c>
       <c r="H98" s="10">
-        <f>IF(OR(COUNT(G98)=0,COUNT(E98)=0,COUNT(F98)=0),"",G98*F98*1000/E98)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I98" s="10">
-        <f>IF(OR(COUNT(E98)=0,COUNT(F98)=0),"",1000*F98/E98)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J98" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K98" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B99" s="6">
         <v>10</v>
@@ -5249,25 +5071,25 @@
         <v>0</v>
       </c>
       <c r="H99" s="10">
-        <f>IF(OR(COUNT(G99)=0,COUNT(E99)=0,COUNT(F99)=0),"",G99*F99*1000/E99)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I99" s="10">
-        <f>IF(OR(COUNT(E99)=0,COUNT(F99)=0),"",1000*F99/E99)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J99" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K99" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B100" s="6">
         <v>10</v>
@@ -5288,25 +5110,25 @@
         <v>0</v>
       </c>
       <c r="H100" s="10">
-        <f>IF(OR(COUNT(G100)=0,COUNT(E100)=0,COUNT(F100)=0),"",G100*F100*1000/E100)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I100" s="10">
-        <f>IF(OR(COUNT(E100)=0,COUNT(F100)=0),"",1000*F100/E100)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J100" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K100" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B101" s="6">
         <v>10</v>
@@ -5327,25 +5149,25 @@
         <v>37</v>
       </c>
       <c r="H101" s="10">
-        <f>IF(OR(COUNT(G101)=0,COUNT(E101)=0,COUNT(F101)=0),"",G101*F101*1000/E101)</f>
+        <f t="shared" si="4"/>
         <v>370000</v>
       </c>
       <c r="I101" s="10">
-        <f>IF(OR(COUNT(E101)=0,COUNT(F101)=0),"",1000*F101/E101)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J101" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K101" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.568201724066995</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B102" s="6">
         <v>10</v>
@@ -5366,25 +5188,25 @@
         <v>54</v>
       </c>
       <c r="H102" s="10">
-        <f>IF(OR(COUNT(G102)=0,COUNT(E102)=0,COUNT(F102)=0),"",G102*F102*1000/E102)</f>
+        <f t="shared" si="4"/>
         <v>540000</v>
       </c>
       <c r="I102" s="10">
-        <f>IF(OR(COUNT(E102)=0,COUNT(F102)=0),"",1000*F102/E102)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J102" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K102" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.7323937598229682</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B103" s="6">
         <v>10</v>
@@ -5405,25 +5227,25 @@
         <v>56</v>
       </c>
       <c r="H103" s="10">
-        <f>IF(OR(COUNT(G103)=0,COUNT(E103)=0,COUNT(F103)=0),"",G103*F103*1000/E103)</f>
+        <f t="shared" si="4"/>
         <v>560000</v>
       </c>
       <c r="I103" s="10">
-        <f>IF(OR(COUNT(E103)=0,COUNT(F103)=0),"",1000*F103/E103)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J103" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K103" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.7481880270062007</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B104" s="6">
         <v>10</v>
@@ -5444,25 +5266,25 @@
         <v>64</v>
       </c>
       <c r="H104" s="10">
-        <f>IF(OR(COUNT(G104)=0,COUNT(E104)=0,COUNT(F104)=0),"",G104*F104*1000/E104)</f>
+        <f t="shared" si="4"/>
         <v>640000</v>
       </c>
       <c r="I104" s="10">
-        <f>IF(OR(COUNT(E104)=0,COUNT(F104)=0),"",1000*F104/E104)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J104" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K104" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.8061799739838875</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B105" s="6">
         <v>10</v>
@@ -5483,25 +5305,25 @@
         <v>51</v>
       </c>
       <c r="H105" s="10">
-        <f>IF(OR(COUNT(G105)=0,COUNT(E105)=0,COUNT(F105)=0),"",G105*F105*1000/E105)</f>
+        <f t="shared" si="4"/>
         <v>51000</v>
       </c>
       <c r="I105" s="10">
-        <f>IF(OR(COUNT(E105)=0,COUNT(F105)=0),"",1000*F105/E105)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J105" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K105" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.7075701760979367</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B106" s="6">
         <v>10</v>
@@ -5522,25 +5344,25 @@
         <v>48</v>
       </c>
       <c r="H106" s="10">
-        <f>IF(OR(COUNT(G106)=0,COUNT(E106)=0,COUNT(F106)=0),"",G106*F106*1000/E106)</f>
+        <f t="shared" si="4"/>
         <v>48000</v>
       </c>
       <c r="I106" s="10">
-        <f>IF(OR(COUNT(E106)=0,COUNT(F106)=0),"",1000*F106/E106)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J106" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K106" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.6812412373755876</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B107" s="6">
         <v>10</v>
@@ -5561,25 +5383,25 @@
         <v>63</v>
       </c>
       <c r="H107" s="10">
-        <f>IF(OR(COUNT(G107)=0,COUNT(E107)=0,COUNT(F107)=0),"",G107*F107*1000/E107)</f>
+        <f t="shared" si="4"/>
         <v>63000</v>
       </c>
       <c r="I107" s="10">
-        <f>IF(OR(COUNT(E107)=0,COUNT(F107)=0),"",1000*F107/E107)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J107" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K107" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.7993405494535821</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B108" s="6">
         <v>10</v>
@@ -5600,25 +5422,25 @@
         <v>70</v>
       </c>
       <c r="H108" s="10">
-        <f>IF(OR(COUNT(G108)=0,COUNT(E108)=0,COUNT(F108)=0),"",G108*F108*1000/E108)</f>
+        <f t="shared" si="4"/>
         <v>70000</v>
       </c>
       <c r="I108" s="10">
-        <f>IF(OR(COUNT(E108)=0,COUNT(F108)=0),"",1000*F108/E108)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J108" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K108" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.8450980400142569</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B109" s="6">
         <v>10</v>
@@ -5639,25 +5461,25 @@
         <v>48</v>
       </c>
       <c r="H109" s="10">
-        <f>IF(OR(COUNT(G109)=0,COUNT(E109)=0,COUNT(F109)=0),"",G109*F109*1000/E109)</f>
+        <f t="shared" si="4"/>
         <v>4800</v>
       </c>
       <c r="I109" s="10">
-        <f>IF(OR(COUNT(E109)=0,COUNT(F109)=0),"",1000*F109/E109)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J109" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K109" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.6812412373755872</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B110" s="6">
         <v>10</v>
@@ -5678,25 +5500,25 @@
         <v>50</v>
       </c>
       <c r="H110" s="10">
-        <f>IF(OR(COUNT(G110)=0,COUNT(E110)=0,COUNT(F110)=0),"",G110*F110*1000/E110)</f>
+        <f t="shared" si="4"/>
         <v>5000</v>
       </c>
       <c r="I110" s="10">
-        <f>IF(OR(COUNT(E110)=0,COUNT(F110)=0),"",1000*F110/E110)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J110" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K110" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.6989700043360187</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B111" s="6">
         <v>10</v>
@@ -5717,25 +5539,25 @@
         <v>43</v>
       </c>
       <c r="H111" s="10">
-        <f>IF(OR(COUNT(G111)=0,COUNT(E111)=0,COUNT(F111)=0),"",G111*F111*1000/E111)</f>
+        <f t="shared" si="4"/>
         <v>4300</v>
       </c>
       <c r="I111" s="10">
-        <f>IF(OR(COUNT(E111)=0,COUNT(F111)=0),"",1000*F111/E111)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J111" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K111" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.6334684555795866</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B112" s="6">
         <v>10</v>
@@ -5756,25 +5578,25 @@
         <v>50</v>
       </c>
       <c r="H112" s="10">
-        <f>IF(OR(COUNT(G112)=0,COUNT(E112)=0,COUNT(F112)=0),"",G112*F112*1000/E112)</f>
+        <f t="shared" si="4"/>
         <v>5000</v>
       </c>
       <c r="I112" s="10">
-        <f>IF(OR(COUNT(E112)=0,COUNT(F112)=0),"",1000*F112/E112)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J112" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K112" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.6989700043360187</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B113" s="6">
         <v>10</v>
@@ -5795,25 +5617,25 @@
         <v>10</v>
       </c>
       <c r="H113" s="10">
-        <f>IF(OR(COUNT(G113)=0,COUNT(E113)=0,COUNT(F113)=0),"",G113*F113*1000/E113)</f>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="I113" s="10">
-        <f>IF(OR(COUNT(E113)=0,COUNT(F113)=0),"",1000*F113/E113)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J113" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K113" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B114" s="6">
         <v>10</v>
@@ -5834,25 +5656,25 @@
         <v>13</v>
       </c>
       <c r="H114" s="10">
-        <f>IF(OR(COUNT(G114)=0,COUNT(E114)=0,COUNT(F114)=0),"",G114*F114*1000/E114)</f>
+        <f t="shared" si="4"/>
         <v>130</v>
       </c>
       <c r="I114" s="10">
-        <f>IF(OR(COUNT(E114)=0,COUNT(F114)=0),"",1000*F114/E114)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J114" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K114" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2.1139433523068369</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B115" s="6">
         <v>10</v>
@@ -5873,25 +5695,25 @@
         <v>1</v>
       </c>
       <c r="H115" s="10">
-        <f>IF(OR(COUNT(G115)=0,COUNT(E115)=0,COUNT(F115)=0),"",G115*F115*1000/E115)</f>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="I115" s="10">
-        <f>IF(OR(COUNT(E115)=0,COUNT(F115)=0),"",1000*F115/E115)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J115" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K115" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B116" s="6">
         <v>10</v>
@@ -5912,25 +5734,25 @@
         <v>2</v>
       </c>
       <c r="H116" s="10">
-        <f>IF(OR(COUNT(G116)=0,COUNT(E116)=0,COUNT(F116)=0),"",G116*F116*1000/E116)</f>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
       <c r="I116" s="10">
-        <f>IF(OR(COUNT(E116)=0,COUNT(F116)=0),"",1000*F116/E116)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J116" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K116" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2.3010299956639813</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B117" s="6">
         <v>10</v>
@@ -5951,25 +5773,25 @@
         <v>0</v>
       </c>
       <c r="H117" s="10">
-        <f>IF(OR(COUNT(G117)=0,COUNT(E117)=0,COUNT(F117)=0),"",G117*F117*1000/E117)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I117" s="10">
-        <f>IF(OR(COUNT(E117)=0,COUNT(F117)=0),"",1000*F117/E117)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J117" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K117" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B118" s="6">
         <v>10</v>
@@ -5990,25 +5812,25 @@
         <v>2</v>
       </c>
       <c r="H118" s="10">
-        <f>IF(OR(COUNT(G118)=0,COUNT(E118)=0,COUNT(F118)=0),"",G118*F118*1000/E118)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="I118" s="10">
-        <f>IF(OR(COUNT(E118)=0,COUNT(F118)=0),"",1000*F118/E118)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J118" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K118" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.3010299956639813</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B119" s="6">
         <v>10</v>
@@ -6029,25 +5851,25 @@
         <v>0</v>
       </c>
       <c r="H119" s="10">
-        <f>IF(OR(COUNT(G119)=0,COUNT(E119)=0,COUNT(F119)=0),"",G119*F119*1000/E119)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I119" s="10">
-        <f>IF(OR(COUNT(E119)=0,COUNT(F119)=0),"",1000*F119/E119)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J119" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K119" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B120" s="6">
         <v>10</v>
@@ -6068,25 +5890,25 @@
         <v>0</v>
       </c>
       <c r="H120" s="10">
-        <f>IF(OR(COUNT(G120)=0,COUNT(E120)=0,COUNT(F120)=0),"",G120*F120*1000/E120)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I120" s="10">
-        <f>IF(OR(COUNT(E120)=0,COUNT(F120)=0),"",1000*F120/E120)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J120" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K120" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B121" s="6">
         <v>10</v>
@@ -6107,25 +5929,25 @@
         <v>0</v>
       </c>
       <c r="H121" s="10">
-        <f>IF(OR(COUNT(G121)=0,COUNT(E121)=0,COUNT(F121)=0),"",G121*F121*1000/E121)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I121" s="10">
-        <f>IF(OR(COUNT(E121)=0,COUNT(F121)=0),"",1000*F121/E121)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J121" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K121" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B122" s="6">
         <v>10</v>
@@ -6146,25 +5968,25 @@
         <v>0</v>
       </c>
       <c r="H122" s="10">
-        <f>IF(OR(COUNT(G122)=0,COUNT(E122)=0,COUNT(F122)=0),"",G122*F122*1000/E122)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I122" s="10">
-        <f>IF(OR(COUNT(E122)=0,COUNT(F122)=0),"",1000*F122/E122)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="J122" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K122" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B123" s="6">
         <v>10</v>
@@ -6185,25 +6007,25 @@
         <v>0</v>
       </c>
       <c r="H123" s="10">
-        <f>IF(OR(COUNT(G123)=0,COUNT(E123)=0,COUNT(F123)=0),"",G123*F123*1000/E123)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I123" s="10">
-        <f>IF(OR(COUNT(E123)=0,COUNT(F123)=0),"",1000*F123/E123)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J123" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K123" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B124" s="6">
         <v>10</v>
@@ -6224,25 +6046,25 @@
         <v>0</v>
       </c>
       <c r="H124" s="10">
-        <f>IF(OR(COUNT(G124)=0,COUNT(E124)=0,COUNT(F124)=0),"",G124*F124*1000/E124)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I124" s="10">
-        <f>IF(OR(COUNT(E124)=0,COUNT(F124)=0),"",1000*F124/E124)</f>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="J124" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>YES</v>
       </c>
       <c r="K124" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B125" s="6">
         <v>10</v>
@@ -6263,25 +6085,25 @@
         <v>62</v>
       </c>
       <c r="H125" s="10">
-        <f>IF(OR(COUNT(G125)=0,COUNT(E125)=0,COUNT(F125)=0),"",G125*F125*1000/E125)</f>
+        <f t="shared" si="4"/>
         <v>620000</v>
       </c>
       <c r="I125" s="10">
-        <f>IF(OR(COUNT(E125)=0,COUNT(F125)=0),"",1000*F125/E125)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J125" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K125" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.7923916894982534</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B126" s="6">
         <v>10</v>
@@ -6302,25 +6124,25 @@
         <v>60</v>
       </c>
       <c r="H126" s="10">
-        <f>IF(OR(COUNT(G126)=0,COUNT(E126)=0,COUNT(F126)=0),"",G126*F126*1000/E126)</f>
+        <f t="shared" si="4"/>
         <v>600000</v>
       </c>
       <c r="I126" s="10">
-        <f>IF(OR(COUNT(E126)=0,COUNT(F126)=0),"",1000*F126/E126)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J126" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K126" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.7781512503836439</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B127" s="6">
         <v>10</v>
@@ -6341,25 +6163,25 @@
         <v>53</v>
       </c>
       <c r="H127" s="10">
-        <f>IF(OR(COUNT(G127)=0,COUNT(E127)=0,COUNT(F127)=0),"",G127*F127*1000/E127)</f>
+        <f t="shared" si="4"/>
         <v>530000</v>
       </c>
       <c r="I127" s="10">
-        <f>IF(OR(COUNT(E127)=0,COUNT(F127)=0),"",1000*F127/E127)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J127" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K127" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.7242758696007892</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B128" s="6">
         <v>10</v>
@@ -6380,25 +6202,25 @@
         <v>55</v>
       </c>
       <c r="H128" s="10">
-        <f>IF(OR(COUNT(G128)=0,COUNT(E128)=0,COUNT(F128)=0),"",G128*F128*1000/E128)</f>
+        <f t="shared" si="4"/>
         <v>550000</v>
       </c>
       <c r="I128" s="10">
-        <f>IF(OR(COUNT(E128)=0,COUNT(F128)=0),"",1000*F128/E128)</f>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="J128" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K128" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.7403626894942441</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B129" s="6">
         <v>10</v>
@@ -6419,25 +6241,25 @@
         <v>46</v>
       </c>
       <c r="H129" s="10">
-        <f>IF(OR(COUNT(G129)=0,COUNT(E129)=0,COUNT(F129)=0),"",G129*F129*1000/E129)</f>
+        <f t="shared" si="4"/>
         <v>46000</v>
       </c>
       <c r="I129" s="10">
-        <f>IF(OR(COUNT(E129)=0,COUNT(F129)=0),"",1000*F129/E129)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J129" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K129" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.6627578316815743</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B130" s="6">
         <v>10</v>
@@ -6458,25 +6280,25 @@
         <v>47</v>
       </c>
       <c r="H130" s="10">
-        <f>IF(OR(COUNT(G130)=0,COUNT(E130)=0,COUNT(F130)=0),"",G130*F130*1000/E130)</f>
+        <f t="shared" si="4"/>
         <v>47000</v>
       </c>
       <c r="I130" s="10">
-        <f>IF(OR(COUNT(E130)=0,COUNT(F130)=0),"",1000*F130/E130)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J130" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K130" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.6720978579357171</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B131" s="6">
         <v>10</v>
@@ -6497,25 +6319,25 @@
         <v>45</v>
       </c>
       <c r="H131" s="10">
-        <f>IF(OR(COUNT(G131)=0,COUNT(E131)=0,COUNT(F131)=0),"",G131*F131*1000/E131)</f>
+        <f t="shared" si="4"/>
         <v>45000</v>
       </c>
       <c r="I131" s="10">
-        <f>IF(OR(COUNT(E131)=0,COUNT(F131)=0),"",1000*F131/E131)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J131" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K131" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.653212513775344</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B132" s="6">
         <v>10</v>
@@ -6536,25 +6358,25 @@
         <v>43</v>
       </c>
       <c r="H132" s="10">
-        <f>IF(OR(COUNT(G132)=0,COUNT(E132)=0,COUNT(F132)=0),"",G132*F132*1000/E132)</f>
+        <f t="shared" si="4"/>
         <v>43000</v>
       </c>
       <c r="I132" s="10">
-        <f>IF(OR(COUNT(E132)=0,COUNT(F132)=0),"",1000*F132/E132)</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="J132" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
       <c r="K132" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.6334684555795862</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B133" s="6">
         <v>10</v>
@@ -6575,25 +6397,25 @@
         <v>55</v>
       </c>
       <c r="H133" s="10">
-        <f>IF(OR(COUNT(G133)=0,COUNT(E133)=0,COUNT(F133)=0),"",G133*F133*1000/E133)</f>
+        <f t="shared" ref="H133:H196" si="8">IF(OR(COUNT(G133)=0,COUNT(E133)=0,COUNT(F133)=0),"",G133*F133*1000/E133)</f>
         <v>5500</v>
       </c>
       <c r="I133" s="10">
-        <f>IF(OR(COUNT(E133)=0,COUNT(F133)=0),"",1000*F133/E133)</f>
+        <f t="shared" ref="I133:I196" si="9">IF(OR(COUNT(E133)=0,COUNT(F133)=0),"",1000*F133/E133)</f>
         <v>100</v>
       </c>
       <c r="J133" s="13" t="str">
-        <f t="shared" ref="J133:J196" si="4">IF(OR(COUNT(H133)=0,COUNT(I133)=0),"",IF(H133&lt;=I133,"YES","no"))</f>
+        <f t="shared" ref="J133:J196" si="10">IF(OR(COUNT(H133)=0,COUNT(I133)=0),"",IF(H133&lt;=I133,"YES","no"))</f>
         <v>no</v>
       </c>
       <c r="K133" s="10">
-        <f t="shared" ref="K133:K196" si="5">IF(OR(COUNT(H133)=0,COUNT(I133)=0),"",LOG10(MAX(H133,I133)))</f>
+        <f t="shared" ref="K133:K196" si="11">IF(OR(COUNT(H133)=0,COUNT(I133)=0),"",LOG10(MAX(H133,I133)))</f>
         <v>3.7403626894942437</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B134" s="6">
         <v>10</v>
@@ -6614,25 +6436,25 @@
         <v>61</v>
       </c>
       <c r="H134" s="10">
-        <f>IF(OR(COUNT(G134)=0,COUNT(E134)=0,COUNT(F134)=0),"",G134*F134*1000/E134)</f>
+        <f t="shared" si="8"/>
         <v>6100</v>
       </c>
       <c r="I134" s="10">
-        <f>IF(OR(COUNT(E134)=0,COUNT(F134)=0),"",1000*F134/E134)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J134" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K134" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.7853298350107671</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B135" s="6">
         <v>10</v>
@@ -6653,25 +6475,25 @@
         <v>51</v>
       </c>
       <c r="H135" s="10">
-        <f>IF(OR(COUNT(G135)=0,COUNT(E135)=0,COUNT(F135)=0),"",G135*F135*1000/E135)</f>
+        <f t="shared" si="8"/>
         <v>5100</v>
       </c>
       <c r="I135" s="10">
-        <f>IF(OR(COUNT(E135)=0,COUNT(F135)=0),"",1000*F135/E135)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J135" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K135" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.7075701760979363</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B136" s="6">
         <v>10</v>
@@ -6692,25 +6514,25 @@
         <v>41</v>
       </c>
       <c r="H136" s="10">
-        <f>IF(OR(COUNT(G136)=0,COUNT(E136)=0,COUNT(F136)=0),"",G136*F136*1000/E136)</f>
+        <f t="shared" si="8"/>
         <v>4100</v>
       </c>
       <c r="I136" s="10">
-        <f>IF(OR(COUNT(E136)=0,COUNT(F136)=0),"",1000*F136/E136)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J136" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K136" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.6127838567197355</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B137" s="6">
         <v>10</v>
@@ -6731,25 +6553,25 @@
         <v>10</v>
       </c>
       <c r="H137" s="10">
-        <f>IF(OR(COUNT(G137)=0,COUNT(E137)=0,COUNT(F137)=0),"",G137*F137*1000/E137)</f>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="I137" s="10">
-        <f>IF(OR(COUNT(E137)=0,COUNT(F137)=0),"",1000*F137/E137)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J137" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K137" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B138" s="6">
         <v>10</v>
@@ -6770,25 +6592,25 @@
         <v>9</v>
       </c>
       <c r="H138" s="10">
-        <f>IF(OR(COUNT(G138)=0,COUNT(E138)=0,COUNT(F138)=0),"",G138*F138*1000/E138)</f>
+        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="I138" s="10">
-        <f>IF(OR(COUNT(E138)=0,COUNT(F138)=0),"",1000*F138/E138)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J138" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K138" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1.954242509439325</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B139" s="6">
         <v>10</v>
@@ -6809,25 +6631,25 @@
         <v>1</v>
       </c>
       <c r="H139" s="10">
-        <f>IF(OR(COUNT(G139)=0,COUNT(E139)=0,COUNT(F139)=0),"",G139*F139*1000/E139)</f>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="I139" s="10">
-        <f>IF(OR(COUNT(E139)=0,COUNT(F139)=0),"",1000*F139/E139)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J139" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K139" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B140" s="6">
         <v>10</v>
@@ -6848,25 +6670,25 @@
         <v>1</v>
       </c>
       <c r="H140" s="10">
-        <f>IF(OR(COUNT(G140)=0,COUNT(E140)=0,COUNT(F140)=0),"",G140*F140*1000/E140)</f>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="I140" s="10">
-        <f>IF(OR(COUNT(E140)=0,COUNT(F140)=0),"",1000*F140/E140)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J140" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K140" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B141" s="6">
         <v>10</v>
@@ -6887,25 +6709,25 @@
         <v>0</v>
       </c>
       <c r="H141" s="10">
-        <f>IF(OR(COUNT(G141)=0,COUNT(E141)=0,COUNT(F141)=0),"",G141*F141*1000/E141)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I141" s="10">
-        <f>IF(OR(COUNT(E141)=0,COUNT(F141)=0),"",1000*F141/E141)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J141" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K141" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B142" s="6">
         <v>10</v>
@@ -6926,25 +6748,25 @@
         <v>0</v>
       </c>
       <c r="H142" s="10">
-        <f>IF(OR(COUNT(G142)=0,COUNT(E142)=0,COUNT(F142)=0),"",G142*F142*1000/E142)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I142" s="10">
-        <f>IF(OR(COUNT(E142)=0,COUNT(F142)=0),"",1000*F142/E142)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J142" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K142" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B143" s="6">
         <v>10</v>
@@ -6965,25 +6787,25 @@
         <v>0</v>
       </c>
       <c r="H143" s="10">
-        <f>IF(OR(COUNT(G143)=0,COUNT(E143)=0,COUNT(F143)=0),"",G143*F143*1000/E143)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I143" s="10">
-        <f>IF(OR(COUNT(E143)=0,COUNT(F143)=0),"",1000*F143/E143)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J143" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K143" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B144" s="6">
         <v>10</v>
@@ -7004,25 +6826,25 @@
         <v>0</v>
       </c>
       <c r="H144" s="10">
-        <f>IF(OR(COUNT(G144)=0,COUNT(E144)=0,COUNT(F144)=0),"",G144*F144*1000/E144)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I144" s="10">
-        <f>IF(OR(COUNT(E144)=0,COUNT(F144)=0),"",1000*F144/E144)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J144" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K144" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B145" s="6">
         <v>10</v>
@@ -7043,25 +6865,25 @@
         <v>1</v>
       </c>
       <c r="H145" s="10">
-        <f>IF(OR(COUNT(G145)=0,COUNT(E145)=0,COUNT(F145)=0),"",G145*F145*1000/E145)</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="I145" s="10">
-        <f>IF(OR(COUNT(E145)=0,COUNT(F145)=0),"",1000*F145/E145)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J145" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K145" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B146" s="6">
         <v>10</v>
@@ -7082,25 +6904,25 @@
         <v>0</v>
       </c>
       <c r="H146" s="10">
-        <f>IF(OR(COUNT(G146)=0,COUNT(E146)=0,COUNT(F146)=0),"",G146*F146*1000/E146)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I146" s="10">
-        <f>IF(OR(COUNT(E146)=0,COUNT(F146)=0),"",1000*F146/E146)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J146" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K146" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B147" s="6">
         <v>10</v>
@@ -7121,25 +6943,25 @@
         <v>0</v>
       </c>
       <c r="H147" s="10">
-        <f>IF(OR(COUNT(G147)=0,COUNT(E147)=0,COUNT(F147)=0),"",G147*F147*1000/E147)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I147" s="10">
-        <f>IF(OR(COUNT(E147)=0,COUNT(F147)=0),"",1000*F147/E147)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J147" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K147" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B148" s="6">
         <v>10</v>
@@ -7160,25 +6982,25 @@
         <v>0</v>
       </c>
       <c r="H148" s="10">
-        <f>IF(OR(COUNT(G148)=0,COUNT(E148)=0,COUNT(F148)=0),"",G148*F148*1000/E148)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I148" s="10">
-        <f>IF(OR(COUNT(E148)=0,COUNT(F148)=0),"",1000*F148/E148)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J148" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K148" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B149" s="6">
         <v>10</v>
@@ -7199,25 +7021,25 @@
         <v>36</v>
       </c>
       <c r="H149" s="10">
-        <f>IF(OR(COUNT(G149)=0,COUNT(E149)=0,COUNT(F149)=0),"",G149*F149*1000/E149)</f>
+        <f t="shared" si="8"/>
         <v>3600000</v>
       </c>
       <c r="I149" s="10">
-        <f>IF(OR(COUNT(E149)=0,COUNT(F149)=0),"",1000*F149/E149)</f>
+        <f t="shared" si="9"/>
         <v>100000</v>
       </c>
       <c r="J149" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K149" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6.5563025007672868</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B150" s="6">
         <v>10</v>
@@ -7238,25 +7060,25 @@
         <v>22</v>
       </c>
       <c r="H150" s="10">
-        <f>IF(OR(COUNT(G150)=0,COUNT(E150)=0,COUNT(F150)=0),"",G150*F150*1000/E150)</f>
+        <f t="shared" si="8"/>
         <v>2200000</v>
       </c>
       <c r="I150" s="10">
-        <f>IF(OR(COUNT(E150)=0,COUNT(F150)=0),"",1000*F150/E150)</f>
+        <f t="shared" si="9"/>
         <v>100000</v>
       </c>
       <c r="J150" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K150" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6.3424226808222066</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B151" s="6">
         <v>10</v>
@@ -7277,25 +7099,25 @@
         <v>33</v>
       </c>
       <c r="H151" s="10">
-        <f>IF(OR(COUNT(G151)=0,COUNT(E151)=0,COUNT(F151)=0),"",G151*F151*1000/E151)</f>
+        <f t="shared" si="8"/>
         <v>3300000</v>
       </c>
       <c r="I151" s="10">
-        <f>IF(OR(COUNT(E151)=0,COUNT(F151)=0),"",1000*F151/E151)</f>
+        <f t="shared" si="9"/>
         <v>100000</v>
       </c>
       <c r="J151" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K151" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6.5185139398778871</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B152" s="6">
         <v>10</v>
@@ -7316,25 +7138,25 @@
         <v>51</v>
       </c>
       <c r="H152" s="10">
-        <f>IF(OR(COUNT(G152)=0,COUNT(E152)=0,COUNT(F152)=0),"",G152*F152*1000/E152)</f>
+        <f t="shared" si="8"/>
         <v>5100000</v>
       </c>
       <c r="I152" s="10">
-        <f>IF(OR(COUNT(E152)=0,COUNT(F152)=0),"",1000*F152/E152)</f>
+        <f t="shared" si="9"/>
         <v>100000</v>
       </c>
       <c r="J152" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K152" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6.7075701760979367</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B153" s="6">
         <v>10</v>
@@ -7355,25 +7177,25 @@
         <v>56</v>
       </c>
       <c r="H153" s="10">
-        <f>IF(OR(COUNT(G153)=0,COUNT(E153)=0,COUNT(F153)=0),"",G153*F153*1000/E153)</f>
+        <f t="shared" si="8"/>
         <v>560000</v>
       </c>
       <c r="I153" s="10">
-        <f>IF(OR(COUNT(E153)=0,COUNT(F153)=0),"",1000*F153/E153)</f>
+        <f t="shared" si="9"/>
         <v>10000</v>
       </c>
       <c r="J153" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K153" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5.7481880270062007</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B154" s="6">
         <v>10</v>
@@ -7394,25 +7216,25 @@
         <v>65</v>
       </c>
       <c r="H154" s="10">
-        <f>IF(OR(COUNT(G154)=0,COUNT(E154)=0,COUNT(F154)=0),"",G154*F154*1000/E154)</f>
+        <f t="shared" si="8"/>
         <v>650000</v>
       </c>
       <c r="I154" s="10">
-        <f>IF(OR(COUNT(E154)=0,COUNT(F154)=0),"",1000*F154/E154)</f>
+        <f t="shared" si="9"/>
         <v>10000</v>
       </c>
       <c r="J154" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K154" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5.8129133566428557</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B155" s="6">
         <v>10</v>
@@ -7433,25 +7255,25 @@
         <v>64</v>
       </c>
       <c r="H155" s="10">
-        <f>IF(OR(COUNT(G155)=0,COUNT(E155)=0,COUNT(F155)=0),"",G155*F155*1000/E155)</f>
+        <f t="shared" si="8"/>
         <v>640000</v>
       </c>
       <c r="I155" s="10">
-        <f>IF(OR(COUNT(E155)=0,COUNT(F155)=0),"",1000*F155/E155)</f>
+        <f t="shared" si="9"/>
         <v>10000</v>
       </c>
       <c r="J155" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K155" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5.8061799739838875</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B156" s="6">
         <v>10</v>
@@ -7472,25 +7294,25 @@
         <v>57</v>
       </c>
       <c r="H156" s="10">
-        <f>IF(OR(COUNT(G156)=0,COUNT(E156)=0,COUNT(F156)=0),"",G156*F156*1000/E156)</f>
+        <f t="shared" si="8"/>
         <v>570000</v>
       </c>
       <c r="I156" s="10">
-        <f>IF(OR(COUNT(E156)=0,COUNT(F156)=0),"",1000*F156/E156)</f>
+        <f t="shared" si="9"/>
         <v>10000</v>
       </c>
       <c r="J156" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K156" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5.7558748556724915</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B157" s="6">
         <v>10</v>
@@ -7511,25 +7333,25 @@
         <v>63</v>
       </c>
       <c r="H157" s="10">
-        <f>IF(OR(COUNT(G157)=0,COUNT(E157)=0,COUNT(F157)=0),"",G157*F157*1000/E157)</f>
+        <f t="shared" si="8"/>
         <v>63000</v>
       </c>
       <c r="I157" s="10">
-        <f>IF(OR(COUNT(E157)=0,COUNT(F157)=0),"",1000*F157/E157)</f>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="J157" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K157" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>4.7993405494535821</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B158" s="6">
         <v>10</v>
@@ -7550,25 +7372,25 @@
         <v>68</v>
       </c>
       <c r="H158" s="10">
-        <f>IF(OR(COUNT(G158)=0,COUNT(E158)=0,COUNT(F158)=0),"",G158*F158*1000/E158)</f>
+        <f t="shared" si="8"/>
         <v>68000</v>
       </c>
       <c r="I158" s="10">
-        <f>IF(OR(COUNT(E158)=0,COUNT(F158)=0),"",1000*F158/E158)</f>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="J158" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K158" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>4.8325089127062366</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B159" s="6">
         <v>10</v>
@@ -7589,25 +7411,25 @@
         <v>69</v>
       </c>
       <c r="H159" s="10">
-        <f>IF(OR(COUNT(G159)=0,COUNT(E159)=0,COUNT(F159)=0),"",G159*F159*1000/E159)</f>
+        <f t="shared" si="8"/>
         <v>69000</v>
       </c>
       <c r="I159" s="10">
-        <f>IF(OR(COUNT(E159)=0,COUNT(F159)=0),"",1000*F159/E159)</f>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="J159" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K159" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>4.8388490907372557</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B160" s="6">
         <v>10</v>
@@ -7628,25 +7450,25 @@
         <v>60</v>
       </c>
       <c r="H160" s="10">
-        <f>IF(OR(COUNT(G160)=0,COUNT(E160)=0,COUNT(F160)=0),"",G160*F160*1000/E160)</f>
+        <f t="shared" si="8"/>
         <v>60000</v>
       </c>
       <c r="I160" s="10">
-        <f>IF(OR(COUNT(E160)=0,COUNT(F160)=0),"",1000*F160/E160)</f>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="J160" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K160" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>4.7781512503836439</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B161" s="6">
         <v>10</v>
@@ -7667,25 +7489,25 @@
         <v>15</v>
       </c>
       <c r="H161" s="10">
-        <f>IF(OR(COUNT(G161)=0,COUNT(E161)=0,COUNT(F161)=0),"",G161*F161*1000/E161)</f>
+        <f t="shared" si="8"/>
         <v>1500</v>
       </c>
       <c r="I161" s="10">
-        <f>IF(OR(COUNT(E161)=0,COUNT(F161)=0),"",1000*F161/E161)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J161" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K161" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.1760912590556813</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B162" s="6">
         <v>10</v>
@@ -7706,25 +7528,25 @@
         <v>15</v>
       </c>
       <c r="H162" s="10">
-        <f>IF(OR(COUNT(G162)=0,COUNT(E162)=0,COUNT(F162)=0),"",G162*F162*1000/E162)</f>
+        <f t="shared" si="8"/>
         <v>1500</v>
       </c>
       <c r="I162" s="10">
-        <f>IF(OR(COUNT(E162)=0,COUNT(F162)=0),"",1000*F162/E162)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J162" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K162" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.1760912590556813</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B163" s="6">
         <v>10</v>
@@ -7745,25 +7567,25 @@
         <v>15</v>
       </c>
       <c r="H163" s="10">
-        <f>IF(OR(COUNT(G163)=0,COUNT(E163)=0,COUNT(F163)=0),"",G163*F163*1000/E163)</f>
+        <f t="shared" si="8"/>
         <v>1500</v>
       </c>
       <c r="I163" s="10">
-        <f>IF(OR(COUNT(E163)=0,COUNT(F163)=0),"",1000*F163/E163)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J163" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K163" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.1760912590556813</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B164" s="6">
         <v>10</v>
@@ -7784,25 +7606,25 @@
         <v>11</v>
       </c>
       <c r="H164" s="10">
-        <f>IF(OR(COUNT(G164)=0,COUNT(E164)=0,COUNT(F164)=0),"",G164*F164*1000/E164)</f>
+        <f t="shared" si="8"/>
         <v>1100</v>
       </c>
       <c r="I164" s="10">
-        <f>IF(OR(COUNT(E164)=0,COUNT(F164)=0),"",1000*F164/E164)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J164" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K164" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.0413926851582249</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B165" s="6">
         <v>10</v>
@@ -7823,25 +7645,25 @@
         <v>13</v>
       </c>
       <c r="H165" s="10">
-        <f>IF(OR(COUNT(G165)=0,COUNT(E165)=0,COUNT(F165)=0),"",G165*F165*1000/E165)</f>
+        <f t="shared" si="8"/>
         <v>130</v>
       </c>
       <c r="I165" s="10">
-        <f>IF(OR(COUNT(E165)=0,COUNT(F165)=0),"",1000*F165/E165)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J165" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K165" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2.1139433523068369</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B166" s="6">
         <v>10</v>
@@ -7862,25 +7684,25 @@
         <v>17</v>
       </c>
       <c r="H166" s="10">
-        <f>IF(OR(COUNT(G166)=0,COUNT(E166)=0,COUNT(F166)=0),"",G166*F166*1000/E166)</f>
+        <f t="shared" si="8"/>
         <v>170</v>
       </c>
       <c r="I166" s="10">
-        <f>IF(OR(COUNT(E166)=0,COUNT(F166)=0),"",1000*F166/E166)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J166" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K166" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2.2304489213782741</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B167" s="6">
         <v>10</v>
@@ -7901,25 +7723,25 @@
         <v>1</v>
       </c>
       <c r="H167" s="10">
-        <f>IF(OR(COUNT(G167)=0,COUNT(E167)=0,COUNT(F167)=0),"",G167*F167*1000/E167)</f>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="I167" s="10">
-        <f>IF(OR(COUNT(E167)=0,COUNT(F167)=0),"",1000*F167/E167)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J167" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K167" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B168" s="6">
         <v>10</v>
@@ -7940,25 +7762,25 @@
         <v>1</v>
       </c>
       <c r="H168" s="10">
-        <f>IF(OR(COUNT(G168)=0,COUNT(E168)=0,COUNT(F168)=0),"",G168*F168*1000/E168)</f>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="I168" s="10">
-        <f>IF(OR(COUNT(E168)=0,COUNT(F168)=0),"",1000*F168/E168)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J168" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K168" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B169" s="6">
         <v>10</v>
@@ -7979,25 +7801,25 @@
         <v>0</v>
       </c>
       <c r="H169" s="10">
-        <f>IF(OR(COUNT(G169)=0,COUNT(E169)=0,COUNT(F169)=0),"",G169*F169*1000/E169)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I169" s="10">
-        <f>IF(OR(COUNT(E169)=0,COUNT(F169)=0),"",1000*F169/E169)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J169" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K169" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B170" s="6">
         <v>10</v>
@@ -8018,25 +7840,25 @@
         <v>1</v>
       </c>
       <c r="H170" s="10">
-        <f>IF(OR(COUNT(G170)=0,COUNT(E170)=0,COUNT(F170)=0),"",G170*F170*1000/E170)</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="I170" s="10">
-        <f>IF(OR(COUNT(E170)=0,COUNT(F170)=0),"",1000*F170/E170)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J170" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K170" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B171" s="6">
         <v>10</v>
@@ -8057,25 +7879,25 @@
         <v>0</v>
       </c>
       <c r="H171" s="10">
-        <f>IF(OR(COUNT(G171)=0,COUNT(E171)=0,COUNT(F171)=0),"",G171*F171*1000/E171)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I171" s="10">
-        <f>IF(OR(COUNT(E171)=0,COUNT(F171)=0),"",1000*F171/E171)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J171" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K171" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B172" s="6">
         <v>10</v>
@@ -8096,25 +7918,25 @@
         <v>0</v>
       </c>
       <c r="H172" s="10">
-        <f>IF(OR(COUNT(G172)=0,COUNT(E172)=0,COUNT(F172)=0),"",G172*F172*1000/E172)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I172" s="10">
-        <f>IF(OR(COUNT(E172)=0,COUNT(F172)=0),"",1000*F172/E172)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J172" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K172" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B173" s="6">
         <v>10</v>
@@ -8135,25 +7957,25 @@
         <v>61</v>
       </c>
       <c r="H173" s="10">
-        <f>IF(OR(COUNT(G173)=0,COUNT(E173)=0,COUNT(F173)=0),"",G173*F173*1000/E173)</f>
+        <f t="shared" si="8"/>
         <v>6100000</v>
       </c>
       <c r="I173" s="10">
-        <f>IF(OR(COUNT(E173)=0,COUNT(F173)=0),"",1000*F173/E173)</f>
+        <f t="shared" si="9"/>
         <v>100000</v>
       </c>
       <c r="J173" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K173" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6.7853298350107671</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B174" s="6">
         <v>10</v>
@@ -8174,25 +7996,25 @@
         <v>48</v>
       </c>
       <c r="H174" s="10">
-        <f>IF(OR(COUNT(G174)=0,COUNT(E174)=0,COUNT(F174)=0),"",G174*F174*1000/E174)</f>
+        <f t="shared" si="8"/>
         <v>4800000</v>
       </c>
       <c r="I174" s="10">
-        <f>IF(OR(COUNT(E174)=0,COUNT(F174)=0),"",1000*F174/E174)</f>
+        <f t="shared" si="9"/>
         <v>100000</v>
       </c>
       <c r="J174" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K174" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6.6812412373755876</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B175" s="6">
         <v>10</v>
@@ -8213,25 +8035,25 @@
         <v>53</v>
       </c>
       <c r="H175" s="10">
-        <f>IF(OR(COUNT(G175)=0,COUNT(E175)=0,COUNT(F175)=0),"",G175*F175*1000/E175)</f>
+        <f t="shared" si="8"/>
         <v>5300000</v>
       </c>
       <c r="I175" s="10">
-        <f>IF(OR(COUNT(E175)=0,COUNT(F175)=0),"",1000*F175/E175)</f>
+        <f t="shared" si="9"/>
         <v>100000</v>
       </c>
       <c r="J175" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K175" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6.7242758696007892</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B176" s="6">
         <v>10</v>
@@ -8252,25 +8074,25 @@
         <v>60</v>
       </c>
       <c r="H176" s="10">
-        <f>IF(OR(COUNT(G176)=0,COUNT(E176)=0,COUNT(F176)=0),"",G176*F176*1000/E176)</f>
+        <f t="shared" si="8"/>
         <v>6000000</v>
       </c>
       <c r="I176" s="10">
-        <f>IF(OR(COUNT(E176)=0,COUNT(F176)=0),"",1000*F176/E176)</f>
+        <f t="shared" si="9"/>
         <v>100000</v>
       </c>
       <c r="J176" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K176" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6.7781512503836439</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B177" s="6">
         <v>10</v>
@@ -8291,25 +8113,25 @@
         <v>56</v>
       </c>
       <c r="H177" s="10">
-        <f>IF(OR(COUNT(G177)=0,COUNT(E177)=0,COUNT(F177)=0),"",G177*F177*1000/E177)</f>
+        <f t="shared" si="8"/>
         <v>560000</v>
       </c>
       <c r="I177" s="10">
-        <f>IF(OR(COUNT(E177)=0,COUNT(F177)=0),"",1000*F177/E177)</f>
+        <f t="shared" si="9"/>
         <v>10000</v>
       </c>
       <c r="J177" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K177" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5.7481880270062007</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B178" s="6">
         <v>10</v>
@@ -8330,25 +8152,25 @@
         <v>66</v>
       </c>
       <c r="H178" s="10">
-        <f>IF(OR(COUNT(G178)=0,COUNT(E178)=0,COUNT(F178)=0),"",G178*F178*1000/E178)</f>
+        <f t="shared" si="8"/>
         <v>660000</v>
       </c>
       <c r="I178" s="10">
-        <f>IF(OR(COUNT(E178)=0,COUNT(F178)=0),"",1000*F178/E178)</f>
+        <f t="shared" si="9"/>
         <v>10000</v>
       </c>
       <c r="J178" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K178" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5.8195439355418683</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B179" s="6">
         <v>10</v>
@@ -8369,25 +8191,25 @@
         <v>51</v>
       </c>
       <c r="H179" s="10">
-        <f>IF(OR(COUNT(G179)=0,COUNT(E179)=0,COUNT(F179)=0),"",G179*F179*1000/E179)</f>
+        <f t="shared" si="8"/>
         <v>510000</v>
       </c>
       <c r="I179" s="10">
-        <f>IF(OR(COUNT(E179)=0,COUNT(F179)=0),"",1000*F179/E179)</f>
+        <f t="shared" si="9"/>
         <v>10000</v>
       </c>
       <c r="J179" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K179" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5.7075701760979367</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B180" s="6">
         <v>10</v>
@@ -8408,25 +8230,25 @@
         <v>56</v>
       </c>
       <c r="H180" s="10">
-        <f>IF(OR(COUNT(G180)=0,COUNT(E180)=0,COUNT(F180)=0),"",G180*F180*1000/E180)</f>
+        <f t="shared" si="8"/>
         <v>560000</v>
       </c>
       <c r="I180" s="10">
-        <f>IF(OR(COUNT(E180)=0,COUNT(F180)=0),"",1000*F180/E180)</f>
+        <f t="shared" si="9"/>
         <v>10000</v>
       </c>
       <c r="J180" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K180" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5.7481880270062007</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B181" s="6">
         <v>10</v>
@@ -8447,25 +8269,25 @@
         <v>62</v>
       </c>
       <c r="H181" s="10">
-        <f>IF(OR(COUNT(G181)=0,COUNT(E181)=0,COUNT(F181)=0),"",G181*F181*1000/E181)</f>
+        <f t="shared" si="8"/>
         <v>62000</v>
       </c>
       <c r="I181" s="10">
-        <f>IF(OR(COUNT(E181)=0,COUNT(F181)=0),"",1000*F181/E181)</f>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="J181" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K181" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>4.7923916894982534</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B182" s="6">
         <v>10</v>
@@ -8486,25 +8308,25 @@
         <v>66</v>
       </c>
       <c r="H182" s="10">
-        <f>IF(OR(COUNT(G182)=0,COUNT(E182)=0,COUNT(F182)=0),"",G182*F182*1000/E182)</f>
+        <f t="shared" si="8"/>
         <v>66000</v>
       </c>
       <c r="I182" s="10">
-        <f>IF(OR(COUNT(E182)=0,COUNT(F182)=0),"",1000*F182/E182)</f>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="J182" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K182" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>4.8195439355418683</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B183" s="6">
         <v>10</v>
@@ -8525,25 +8347,25 @@
         <v>57</v>
       </c>
       <c r="H183" s="10">
-        <f>IF(OR(COUNT(G183)=0,COUNT(E183)=0,COUNT(F183)=0),"",G183*F183*1000/E183)</f>
+        <f t="shared" si="8"/>
         <v>57000</v>
       </c>
       <c r="I183" s="10">
-        <f>IF(OR(COUNT(E183)=0,COUNT(F183)=0),"",1000*F183/E183)</f>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="J183" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K183" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>4.7558748556724915</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B184" s="6">
         <v>10</v>
@@ -8564,25 +8386,25 @@
         <v>59</v>
       </c>
       <c r="H184" s="10">
-        <f>IF(OR(COUNT(G184)=0,COUNT(E184)=0,COUNT(F184)=0),"",G184*F184*1000/E184)</f>
+        <f t="shared" si="8"/>
         <v>59000</v>
       </c>
       <c r="I184" s="10">
-        <f>IF(OR(COUNT(E184)=0,COUNT(F184)=0),"",1000*F184/E184)</f>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="J184" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K184" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>4.7708520116421438</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B185" s="6">
         <v>10</v>
@@ -8603,25 +8425,25 @@
         <v>134</v>
       </c>
       <c r="H185" s="10">
-        <f>IF(OR(COUNT(G185)=0,COUNT(E185)=0,COUNT(F185)=0),"",G185*F185*1000/E185)</f>
+        <f t="shared" si="8"/>
         <v>1340</v>
       </c>
       <c r="I185" s="10">
-        <f>IF(OR(COUNT(E185)=0,COUNT(F185)=0),"",1000*F185/E185)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J185" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K185" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.1271047983648077</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B186" s="6">
         <v>10</v>
@@ -8642,25 +8464,25 @@
         <v>154</v>
       </c>
       <c r="H186" s="10">
-        <f>IF(OR(COUNT(G186)=0,COUNT(E186)=0,COUNT(F186)=0),"",G186*F186*1000/E186)</f>
+        <f t="shared" si="8"/>
         <v>1540</v>
       </c>
       <c r="I186" s="10">
-        <f>IF(OR(COUNT(E186)=0,COUNT(F186)=0),"",1000*F186/E186)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J186" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K186" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.1875207208364631</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B187" s="6">
         <v>10</v>
@@ -8681,25 +8503,25 @@
         <v>14</v>
       </c>
       <c r="H187" s="10">
-        <f>IF(OR(COUNT(G187)=0,COUNT(E187)=0,COUNT(F187)=0),"",G187*F187*1000/E187)</f>
+        <f t="shared" si="8"/>
         <v>1400</v>
       </c>
       <c r="I187" s="10">
-        <f>IF(OR(COUNT(E187)=0,COUNT(F187)=0),"",1000*F187/E187)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J187" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K187" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.1461280356782382</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B188" s="6">
         <v>10</v>
@@ -8720,25 +8542,25 @@
         <v>13</v>
       </c>
       <c r="H188" s="10">
-        <f>IF(OR(COUNT(G188)=0,COUNT(E188)=0,COUNT(F188)=0),"",G188*F188*1000/E188)</f>
+        <f t="shared" si="8"/>
         <v>1300</v>
       </c>
       <c r="I188" s="10">
-        <f>IF(OR(COUNT(E188)=0,COUNT(F188)=0),"",1000*F188/E188)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J188" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K188" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3.1139433523068369</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B189" s="6">
         <v>10</v>
@@ -8759,25 +8581,25 @@
         <v>6</v>
       </c>
       <c r="H189" s="10">
-        <f>IF(OR(COUNT(G189)=0,COUNT(E189)=0,COUNT(F189)=0),"",G189*F189*1000/E189)</f>
+        <f t="shared" si="8"/>
         <v>60</v>
       </c>
       <c r="I189" s="10">
-        <f>IF(OR(COUNT(E189)=0,COUNT(F189)=0),"",1000*F189/E189)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J189" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K189" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1.7781512503836436</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B190" s="6">
         <v>10</v>
@@ -8798,25 +8620,25 @@
         <v>12</v>
       </c>
       <c r="H190" s="10">
-        <f>IF(OR(COUNT(G190)=0,COUNT(E190)=0,COUNT(F190)=0),"",G190*F190*1000/E190)</f>
+        <f t="shared" si="8"/>
         <v>120</v>
       </c>
       <c r="I190" s="10">
-        <f>IF(OR(COUNT(E190)=0,COUNT(F190)=0),"",1000*F190/E190)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J190" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>no</v>
       </c>
       <c r="K190" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2.0791812460476247</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B191" s="6">
         <v>10</v>
@@ -8837,25 +8659,25 @@
         <v>0</v>
       </c>
       <c r="H191" s="10">
-        <f>IF(OR(COUNT(G191)=0,COUNT(E191)=0,COUNT(F191)=0),"",G191*F191*1000/E191)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I191" s="10">
-        <f>IF(OR(COUNT(E191)=0,COUNT(F191)=0),"",1000*F191/E191)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J191" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K191" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B192" s="6">
         <v>10</v>
@@ -8876,25 +8698,25 @@
         <v>1</v>
       </c>
       <c r="H192" s="10">
-        <f>IF(OR(COUNT(G192)=0,COUNT(E192)=0,COUNT(F192)=0),"",G192*F192*1000/E192)</f>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="I192" s="10">
-        <f>IF(OR(COUNT(E192)=0,COUNT(F192)=0),"",1000*F192/E192)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J192" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K192" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B193" s="6">
         <v>10</v>
@@ -8915,25 +8737,25 @@
         <v>0</v>
       </c>
       <c r="H193" s="10">
-        <f>IF(OR(COUNT(G193)=0,COUNT(E193)=0,COUNT(F193)=0),"",G193*F193*1000/E193)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I193" s="10">
-        <f>IF(OR(COUNT(E193)=0,COUNT(F193)=0),"",1000*F193/E193)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J193" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K193" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B194" s="6">
         <v>10</v>
@@ -8954,25 +8776,25 @@
         <v>0</v>
       </c>
       <c r="H194" s="10">
-        <f>IF(OR(COUNT(G194)=0,COUNT(E194)=0,COUNT(F194)=0),"",G194*F194*1000/E194)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I194" s="10">
-        <f>IF(OR(COUNT(E194)=0,COUNT(F194)=0),"",1000*F194/E194)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J194" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K194" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B195" s="6">
         <v>10</v>
@@ -8993,25 +8815,25 @@
         <v>0</v>
       </c>
       <c r="H195" s="10">
-        <f>IF(OR(COUNT(G195)=0,COUNT(E195)=0,COUNT(F195)=0),"",G195*F195*1000/E195)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I195" s="10">
-        <f>IF(OR(COUNT(E195)=0,COUNT(F195)=0),"",1000*F195/E195)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J195" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K195" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B196" s="6">
         <v>10</v>
@@ -9032,25 +8854,25 @@
         <v>0</v>
       </c>
       <c r="H196" s="10">
-        <f>IF(OR(COUNT(G196)=0,COUNT(E196)=0,COUNT(F196)=0),"",G196*F196*1000/E196)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I196" s="10">
-        <f>IF(OR(COUNT(E196)=0,COUNT(F196)=0),"",1000*F196/E196)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="J196" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>YES</v>
       </c>
       <c r="K196" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B197" s="6">
         <v>10</v>
@@ -9071,25 +8893,25 @@
         <v>62</v>
       </c>
       <c r="H197" s="10">
-        <f>IF(OR(COUNT(G197)=0,COUNT(E197)=0,COUNT(F197)=0),"",G197*F197*1000/E197)</f>
+        <f t="shared" ref="H197:H260" si="12">IF(OR(COUNT(G197)=0,COUNT(E197)=0,COUNT(F197)=0),"",G197*F197*1000/E197)</f>
         <v>6200000</v>
       </c>
       <c r="I197" s="10">
-        <f>IF(OR(COUNT(E197)=0,COUNT(F197)=0),"",1000*F197/E197)</f>
+        <f t="shared" ref="I197:I220" si="13">IF(OR(COUNT(E197)=0,COUNT(F197)=0),"",1000*F197/E197)</f>
         <v>100000</v>
       </c>
       <c r="J197" s="13" t="str">
-        <f t="shared" ref="J197:J220" si="6">IF(OR(COUNT(H197)=0,COUNT(I197)=0),"",IF(H197&lt;=I197,"YES","no"))</f>
+        <f t="shared" ref="J197:J220" si="14">IF(OR(COUNT(H197)=0,COUNT(I197)=0),"",IF(H197&lt;=I197,"YES","no"))</f>
         <v>no</v>
       </c>
       <c r="K197" s="10">
-        <f t="shared" ref="K197:K220" si="7">IF(OR(COUNT(H197)=0,COUNT(I197)=0),"",LOG10(MAX(H197,I197)))</f>
+        <f t="shared" ref="K197:K220" si="15">IF(OR(COUNT(H197)=0,COUNT(I197)=0),"",LOG10(MAX(H197,I197)))</f>
         <v>6.7923916894982534</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B198" s="6">
         <v>10</v>
@@ -9110,25 +8932,25 @@
         <v>64</v>
       </c>
       <c r="H198" s="10">
-        <f>IF(OR(COUNT(G198)=0,COUNT(E198)=0,COUNT(F198)=0),"",G198*F198*1000/E198)</f>
+        <f t="shared" si="12"/>
         <v>6400000</v>
       </c>
       <c r="I198" s="10">
-        <f>IF(OR(COUNT(E198)=0,COUNT(F198)=0),"",1000*F198/E198)</f>
+        <f t="shared" si="13"/>
         <v>100000</v>
       </c>
       <c r="J198" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K198" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>6.8061799739838875</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B199" s="6">
         <v>10</v>
@@ -9149,25 +8971,25 @@
         <v>55</v>
       </c>
       <c r="H199" s="10">
-        <f>IF(OR(COUNT(G199)=0,COUNT(E199)=0,COUNT(F199)=0),"",G199*F199*1000/E199)</f>
+        <f t="shared" si="12"/>
         <v>5500000</v>
       </c>
       <c r="I199" s="10">
-        <f>IF(OR(COUNT(E199)=0,COUNT(F199)=0),"",1000*F199/E199)</f>
+        <f t="shared" si="13"/>
         <v>100000</v>
       </c>
       <c r="J199" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K199" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>6.7403626894942441</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B200" s="6">
         <v>10</v>
@@ -9188,25 +9010,25 @@
         <v>52</v>
       </c>
       <c r="H200" s="10">
-        <f>IF(OR(COUNT(G200)=0,COUNT(E200)=0,COUNT(F200)=0),"",G200*F200*1000/E200)</f>
+        <f t="shared" si="12"/>
         <v>5200000</v>
       </c>
       <c r="I200" s="10">
-        <f>IF(OR(COUNT(E200)=0,COUNT(F200)=0),"",1000*F200/E200)</f>
+        <f t="shared" si="13"/>
         <v>100000</v>
       </c>
       <c r="J200" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K200" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>6.7160033436347994</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B201" s="6">
         <v>10</v>
@@ -9227,25 +9049,25 @@
         <v>57</v>
       </c>
       <c r="H201" s="10">
-        <f>IF(OR(COUNT(G201)=0,COUNT(E201)=0,COUNT(F201)=0),"",G201*F201*1000/E201)</f>
+        <f t="shared" si="12"/>
         <v>570000</v>
       </c>
       <c r="I201" s="10">
-        <f>IF(OR(COUNT(E201)=0,COUNT(F201)=0),"",1000*F201/E201)</f>
+        <f t="shared" si="13"/>
         <v>10000</v>
       </c>
       <c r="J201" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K201" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>5.7558748556724915</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B202" s="6">
         <v>10</v>
@@ -9266,25 +9088,25 @@
         <v>50</v>
       </c>
       <c r="H202" s="10">
-        <f>IF(OR(COUNT(G202)=0,COUNT(E202)=0,COUNT(F202)=0),"",G202*F202*1000/E202)</f>
+        <f t="shared" si="12"/>
         <v>500000</v>
       </c>
       <c r="I202" s="10">
-        <f>IF(OR(COUNT(E202)=0,COUNT(F202)=0),"",1000*F202/E202)</f>
+        <f t="shared" si="13"/>
         <v>10000</v>
       </c>
       <c r="J202" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K202" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>5.6989700043360187</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B203" s="6">
         <v>10</v>
@@ -9305,25 +9127,25 @@
         <v>47</v>
       </c>
       <c r="H203" s="10">
-        <f>IF(OR(COUNT(G203)=0,COUNT(E203)=0,COUNT(F203)=0),"",G203*F203*1000/E203)</f>
+        <f t="shared" si="12"/>
         <v>470000</v>
       </c>
       <c r="I203" s="10">
-        <f>IF(OR(COUNT(E203)=0,COUNT(F203)=0),"",1000*F203/E203)</f>
+        <f t="shared" si="13"/>
         <v>10000</v>
       </c>
       <c r="J203" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K203" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>5.6720978579357171</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B204" s="6">
         <v>10</v>
@@ -9344,25 +9166,25 @@
         <v>62</v>
       </c>
       <c r="H204" s="10">
-        <f>IF(OR(COUNT(G204)=0,COUNT(E204)=0,COUNT(F204)=0),"",G204*F204*1000/E204)</f>
+        <f t="shared" si="12"/>
         <v>620000</v>
       </c>
       <c r="I204" s="10">
-        <f>IF(OR(COUNT(E204)=0,COUNT(F204)=0),"",1000*F204/E204)</f>
+        <f t="shared" si="13"/>
         <v>10000</v>
       </c>
       <c r="J204" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K204" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>5.7923916894982534</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B205" s="6">
         <v>10</v>
@@ -9383,25 +9205,25 @@
         <v>48</v>
       </c>
       <c r="H205" s="10">
-        <f>IF(OR(COUNT(G205)=0,COUNT(E205)=0,COUNT(F205)=0),"",G205*F205*1000/E205)</f>
+        <f t="shared" si="12"/>
         <v>48000</v>
       </c>
       <c r="I205" s="10">
-        <f>IF(OR(COUNT(E205)=0,COUNT(F205)=0),"",1000*F205/E205)</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="J205" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K205" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>4.6812412373755876</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B206" s="6">
         <v>10</v>
@@ -9422,25 +9244,25 @@
         <v>46</v>
       </c>
       <c r="H206" s="10">
-        <f>IF(OR(COUNT(G206)=0,COUNT(E206)=0,COUNT(F206)=0),"",G206*F206*1000/E206)</f>
+        <f t="shared" si="12"/>
         <v>46000</v>
       </c>
       <c r="I206" s="10">
-        <f>IF(OR(COUNT(E206)=0,COUNT(F206)=0),"",1000*F206/E206)</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="J206" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K206" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>4.6627578316815743</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B207" s="6">
         <v>10</v>
@@ -9461,25 +9283,25 @@
         <v>39</v>
       </c>
       <c r="H207" s="10">
-        <f>IF(OR(COUNT(G207)=0,COUNT(E207)=0,COUNT(F207)=0),"",G207*F207*1000/E207)</f>
+        <f t="shared" si="12"/>
         <v>39000</v>
       </c>
       <c r="I207" s="10">
-        <f>IF(OR(COUNT(E207)=0,COUNT(F207)=0),"",1000*F207/E207)</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="J207" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K207" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>4.5910646070264995</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B208" s="6">
         <v>10</v>
@@ -9500,25 +9322,25 @@
         <v>51</v>
       </c>
       <c r="H208" s="10">
-        <f>IF(OR(COUNT(G208)=0,COUNT(E208)=0,COUNT(F208)=0),"",G208*F208*1000/E208)</f>
+        <f t="shared" si="12"/>
         <v>51000</v>
       </c>
       <c r="I208" s="10">
-        <f>IF(OR(COUNT(E208)=0,COUNT(F208)=0),"",1000*F208/E208)</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="J208" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K208" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>4.7075701760979367</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B209" s="6">
         <v>10</v>
@@ -9539,25 +9361,25 @@
         <v>109</v>
       </c>
       <c r="H209" s="10">
-        <f>IF(OR(COUNT(G209)=0,COUNT(E209)=0,COUNT(F209)=0),"",G209*F209*1000/E209)</f>
+        <f t="shared" si="12"/>
         <v>1090</v>
       </c>
       <c r="I209" s="10">
-        <f>IF(OR(COUNT(E209)=0,COUNT(F209)=0),"",1000*F209/E209)</f>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="J209" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K209" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>3.0374264979406238</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B210" s="6">
         <v>10</v>
@@ -9578,25 +9400,25 @@
         <v>125</v>
       </c>
       <c r="H210" s="10">
-        <f>IF(OR(COUNT(G210)=0,COUNT(E210)=0,COUNT(F210)=0),"",G210*F210*1000/E210)</f>
+        <f t="shared" si="12"/>
         <v>1250</v>
       </c>
       <c r="I210" s="10">
-        <f>IF(OR(COUNT(E210)=0,COUNT(F210)=0),"",1000*F210/E210)</f>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="J210" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K210" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>3.0969100130080562</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B211" s="6">
         <v>10</v>
@@ -9617,25 +9439,25 @@
         <v>10</v>
       </c>
       <c r="H211" s="10">
-        <f>IF(OR(COUNT(G211)=0,COUNT(E211)=0,COUNT(F211)=0),"",G211*F211*1000/E211)</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="I211" s="10">
-        <f>IF(OR(COUNT(E211)=0,COUNT(F211)=0),"",1000*F211/E211)</f>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="J211" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K211" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B212" s="6">
         <v>10</v>
@@ -9656,25 +9478,25 @@
         <v>9</v>
       </c>
       <c r="H212" s="10">
-        <f>IF(OR(COUNT(G212)=0,COUNT(E212)=0,COUNT(F212)=0),"",G212*F212*1000/E212)</f>
+        <f t="shared" si="12"/>
         <v>900</v>
       </c>
       <c r="I212" s="10">
-        <f>IF(OR(COUNT(E212)=0,COUNT(F212)=0),"",1000*F212/E212)</f>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="J212" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K212" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>2.9542425094393248</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B213" s="6">
         <v>10</v>
@@ -9695,25 +9517,25 @@
         <v>7</v>
       </c>
       <c r="H213" s="10">
-        <f>IF(OR(COUNT(G213)=0,COUNT(E213)=0,COUNT(F213)=0),"",G213*F213*1000/E213)</f>
+        <f t="shared" si="12"/>
         <v>70</v>
       </c>
       <c r="I213" s="10">
-        <f>IF(OR(COUNT(E213)=0,COUNT(F213)=0),"",1000*F213/E213)</f>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="J213" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K213" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>1.8450980400142569</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B214" s="6">
         <v>10</v>
@@ -9734,25 +9556,25 @@
         <v>6</v>
       </c>
       <c r="H214" s="10">
-        <f>IF(OR(COUNT(G214)=0,COUNT(E214)=0,COUNT(F214)=0),"",G214*F214*1000/E214)</f>
+        <f t="shared" si="12"/>
         <v>60</v>
       </c>
       <c r="I214" s="10">
-        <f>IF(OR(COUNT(E214)=0,COUNT(F214)=0),"",1000*F214/E214)</f>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="J214" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K214" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>1.7781512503836436</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B215" s="6">
         <v>10</v>
@@ -9773,25 +9595,25 @@
         <v>1</v>
       </c>
       <c r="H215" s="10">
-        <f>IF(OR(COUNT(G215)=0,COUNT(E215)=0,COUNT(F215)=0),"",G215*F215*1000/E215)</f>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
       <c r="I215" s="10">
-        <f>IF(OR(COUNT(E215)=0,COUNT(F215)=0),"",1000*F215/E215)</f>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="J215" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>YES</v>
       </c>
       <c r="K215" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B216" s="6">
         <v>10</v>
@@ -9812,25 +9634,25 @@
         <v>0</v>
       </c>
       <c r="H216" s="10">
-        <f>IF(OR(COUNT(G216)=0,COUNT(E216)=0,COUNT(F216)=0),"",G216*F216*1000/E216)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I216" s="10">
-        <f>IF(OR(COUNT(E216)=0,COUNT(F216)=0),"",1000*F216/E216)</f>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="J216" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>YES</v>
       </c>
       <c r="K216" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B217" s="6">
         <v>10</v>
@@ -9851,25 +9673,25 @@
         <v>0</v>
       </c>
       <c r="H217" s="10">
-        <f>IF(OR(COUNT(G217)=0,COUNT(E217)=0,COUNT(F217)=0),"",G217*F217*1000/E217)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I217" s="10">
-        <f>IF(OR(COUNT(E217)=0,COUNT(F217)=0),"",1000*F217/E217)</f>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="J217" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>YES</v>
       </c>
       <c r="K217" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B218" s="6">
         <v>10</v>
@@ -9890,25 +9712,25 @@
         <v>2</v>
       </c>
       <c r="H218" s="10">
-        <f>IF(OR(COUNT(G218)=0,COUNT(E218)=0,COUNT(F218)=0),"",G218*F218*1000/E218)</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="I218" s="10">
-        <f>IF(OR(COUNT(E218)=0,COUNT(F218)=0),"",1000*F218/E218)</f>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="J218" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>no</v>
       </c>
       <c r="K218" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>1.3010299956639813</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B219" s="6">
         <v>10</v>
@@ -9929,25 +9751,25 @@
         <v>0</v>
       </c>
       <c r="H219" s="10">
-        <f>IF(OR(COUNT(G219)=0,COUNT(E219)=0,COUNT(F219)=0),"",G219*F219*1000/E219)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I219" s="10">
-        <f>IF(OR(COUNT(E219)=0,COUNT(F219)=0),"",1000*F219/E219)</f>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="J219" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>YES</v>
       </c>
       <c r="K219" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B220" s="6">
         <v>10</v>
@@ -9968,619 +9790,619 @@
         <v>0</v>
       </c>
       <c r="H220" s="10">
-        <f>IF(OR(COUNT(G220)=0,COUNT(E220)=0,COUNT(F220)=0),"",G220*F220*1000/E220)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I220" s="10">
-        <f>IF(OR(COUNT(E220)=0,COUNT(F220)=0),"",1000*F220/E220)</f>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="J220" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>YES</v>
       </c>
       <c r="K220" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A221" s="16"/>
-      <c r="B221" s="16"/>
-      <c r="C221" s="16"/>
-      <c r="D221" s="16"/>
-      <c r="E221" s="16"/>
-      <c r="F221" s="16"/>
-      <c r="G221" s="16"/>
+      <c r="A221" s="15"/>
+      <c r="B221" s="15"/>
+      <c r="C221" s="15"/>
+      <c r="D221" s="15"/>
+      <c r="E221" s="15"/>
+      <c r="F221" s="15"/>
+      <c r="G221" s="15"/>
       <c r="H221" s="10" t="str">
-        <f>IF(OR(G221="",E221="",F221=""),"",G221*F221*1000/E221)</f>
+        <f t="shared" ref="H221:H244" si="16">IF(OR(G221="",E221="",F221=""),"",G221*F221*1000/E221)</f>
         <v/>
       </c>
       <c r="I221" s="10" t="str">
-        <f>IF(E221="","",1000/E221)</f>
+        <f t="shared" ref="I221:I244" si="17">IF(E221="","",1000/E221)</f>
         <v/>
       </c>
       <c r="J221" s="13" t="str">
-        <f t="shared" ref="J221:J244" si="8">IF(OR(H221="",I221=""),"",IF(H221&lt;=I221,"YES","no"))</f>
+        <f t="shared" ref="J221:J244" si="18">IF(OR(H221="",I221=""),"",IF(H221&lt;=I221,"YES","no"))</f>
         <v/>
       </c>
       <c r="K221" s="10" t="str">
-        <f t="shared" ref="K221:K244" si="9">IF(OR(H221="",H221&lt;=0),"",LOG10(H221))</f>
+        <f t="shared" ref="K221:K244" si="19">IF(OR(H221="",H221&lt;=0),"",LOG10(H221))</f>
         <v/>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A222" s="16"/>
-      <c r="B222" s="16"/>
-      <c r="C222" s="16"/>
-      <c r="D222" s="16"/>
-      <c r="E222" s="16"/>
-      <c r="F222" s="16"/>
-      <c r="G222" s="16"/>
+      <c r="A222" s="15"/>
+      <c r="B222" s="15"/>
+      <c r="C222" s="15"/>
+      <c r="D222" s="15"/>
+      <c r="E222" s="15"/>
+      <c r="F222" s="15"/>
+      <c r="G222" s="15"/>
       <c r="H222" s="10" t="str">
-        <f>IF(OR(G222="",E222="",F222=""),"",G222*F222*1000/E222)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I222" s="10" t="str">
-        <f>IF(E222="","",1000/E222)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J222" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K222" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A223" s="16"/>
-      <c r="B223" s="16"/>
-      <c r="C223" s="16"/>
-      <c r="D223" s="16"/>
-      <c r="E223" s="16"/>
-      <c r="F223" s="16"/>
-      <c r="G223" s="16"/>
+      <c r="A223" s="15"/>
+      <c r="B223" s="15"/>
+      <c r="C223" s="15"/>
+      <c r="D223" s="15"/>
+      <c r="E223" s="15"/>
+      <c r="F223" s="15"/>
+      <c r="G223" s="15"/>
       <c r="H223" s="10" t="str">
-        <f>IF(OR(G223="",E223="",F223=""),"",G223*F223*1000/E223)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I223" s="10" t="str">
-        <f>IF(E223="","",1000/E223)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J223" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K223" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A224" s="16"/>
-      <c r="B224" s="16"/>
-      <c r="C224" s="16"/>
-      <c r="D224" s="16"/>
-      <c r="E224" s="16"/>
-      <c r="F224" s="16"/>
-      <c r="G224" s="16"/>
+      <c r="A224" s="15"/>
+      <c r="B224" s="15"/>
+      <c r="C224" s="15"/>
+      <c r="D224" s="15"/>
+      <c r="E224" s="15"/>
+      <c r="F224" s="15"/>
+      <c r="G224" s="15"/>
       <c r="H224" s="10" t="str">
-        <f>IF(OR(G224="",E224="",F224=""),"",G224*F224*1000/E224)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I224" s="10" t="str">
-        <f>IF(E224="","",1000/E224)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J224" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K224" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A225" s="16"/>
-      <c r="B225" s="16"/>
-      <c r="C225" s="16"/>
-      <c r="D225" s="16"/>
-      <c r="E225" s="16"/>
-      <c r="F225" s="16"/>
-      <c r="G225" s="16"/>
+      <c r="A225" s="15"/>
+      <c r="B225" s="15"/>
+      <c r="C225" s="15"/>
+      <c r="D225" s="15"/>
+      <c r="E225" s="15"/>
+      <c r="F225" s="15"/>
+      <c r="G225" s="15"/>
       <c r="H225" s="10" t="str">
-        <f>IF(OR(G225="",E225="",F225=""),"",G225*F225*1000/E225)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I225" s="10" t="str">
-        <f>IF(E225="","",1000/E225)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J225" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K225" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A226" s="16"/>
-      <c r="B226" s="16"/>
-      <c r="C226" s="16"/>
-      <c r="D226" s="16"/>
-      <c r="E226" s="16"/>
-      <c r="F226" s="16"/>
-      <c r="G226" s="16"/>
+      <c r="A226" s="15"/>
+      <c r="B226" s="15"/>
+      <c r="C226" s="15"/>
+      <c r="D226" s="15"/>
+      <c r="E226" s="15"/>
+      <c r="F226" s="15"/>
+      <c r="G226" s="15"/>
       <c r="H226" s="10" t="str">
-        <f>IF(OR(G226="",E226="",F226=""),"",G226*F226*1000/E226)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I226" s="10" t="str">
-        <f>IF(E226="","",1000/E226)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J226" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K226" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A227" s="16"/>
-      <c r="B227" s="16"/>
-      <c r="C227" s="16"/>
-      <c r="D227" s="16"/>
-      <c r="E227" s="16"/>
-      <c r="F227" s="16"/>
-      <c r="G227" s="16"/>
+      <c r="A227" s="15"/>
+      <c r="B227" s="15"/>
+      <c r="C227" s="15"/>
+      <c r="D227" s="15"/>
+      <c r="E227" s="15"/>
+      <c r="F227" s="15"/>
+      <c r="G227" s="15"/>
       <c r="H227" s="10" t="str">
-        <f>IF(OR(G227="",E227="",F227=""),"",G227*F227*1000/E227)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I227" s="10" t="str">
-        <f>IF(E227="","",1000/E227)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J227" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K227" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A228" s="16"/>
-      <c r="B228" s="16"/>
-      <c r="C228" s="16"/>
-      <c r="D228" s="16"/>
-      <c r="E228" s="16"/>
-      <c r="F228" s="16"/>
-      <c r="G228" s="16"/>
+      <c r="A228" s="15"/>
+      <c r="B228" s="15"/>
+      <c r="C228" s="15"/>
+      <c r="D228" s="15"/>
+      <c r="E228" s="15"/>
+      <c r="F228" s="15"/>
+      <c r="G228" s="15"/>
       <c r="H228" s="10" t="str">
-        <f>IF(OR(G228="",E228="",F228=""),"",G228*F228*1000/E228)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I228" s="10" t="str">
-        <f>IF(E228="","",1000/E228)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J228" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K228" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A229" s="16"/>
-      <c r="B229" s="16"/>
-      <c r="C229" s="16"/>
-      <c r="D229" s="16"/>
-      <c r="E229" s="16"/>
-      <c r="F229" s="16"/>
-      <c r="G229" s="16"/>
+      <c r="A229" s="15"/>
+      <c r="B229" s="15"/>
+      <c r="C229" s="15"/>
+      <c r="D229" s="15"/>
+      <c r="E229" s="15"/>
+      <c r="F229" s="15"/>
+      <c r="G229" s="15"/>
       <c r="H229" s="10" t="str">
-        <f>IF(OR(G229="",E229="",F229=""),"",G229*F229*1000/E229)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I229" s="10" t="str">
-        <f>IF(E229="","",1000/E229)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J229" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K229" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A230" s="16"/>
-      <c r="B230" s="16"/>
-      <c r="C230" s="16"/>
-      <c r="D230" s="16"/>
-      <c r="E230" s="16"/>
-      <c r="F230" s="16"/>
-      <c r="G230" s="16"/>
+      <c r="A230" s="15"/>
+      <c r="B230" s="15"/>
+      <c r="C230" s="15"/>
+      <c r="D230" s="15"/>
+      <c r="E230" s="15"/>
+      <c r="F230" s="15"/>
+      <c r="G230" s="15"/>
       <c r="H230" s="10" t="str">
-        <f>IF(OR(G230="",E230="",F230=""),"",G230*F230*1000/E230)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I230" s="10" t="str">
-        <f>IF(E230="","",1000/E230)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J230" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K230" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A231" s="16"/>
-      <c r="B231" s="16"/>
-      <c r="C231" s="16"/>
-      <c r="D231" s="16"/>
-      <c r="E231" s="16"/>
-      <c r="F231" s="16"/>
-      <c r="G231" s="16"/>
+      <c r="A231" s="15"/>
+      <c r="B231" s="15"/>
+      <c r="C231" s="15"/>
+      <c r="D231" s="15"/>
+      <c r="E231" s="15"/>
+      <c r="F231" s="15"/>
+      <c r="G231" s="15"/>
       <c r="H231" s="10" t="str">
-        <f>IF(OR(G231="",E231="",F231=""),"",G231*F231*1000/E231)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I231" s="10" t="str">
-        <f>IF(E231="","",1000/E231)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J231" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K231" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A232" s="16"/>
-      <c r="B232" s="16"/>
-      <c r="C232" s="16"/>
-      <c r="D232" s="16"/>
-      <c r="E232" s="16"/>
-      <c r="F232" s="16"/>
-      <c r="G232" s="16"/>
+      <c r="A232" s="15"/>
+      <c r="B232" s="15"/>
+      <c r="C232" s="15"/>
+      <c r="D232" s="15"/>
+      <c r="E232" s="15"/>
+      <c r="F232" s="15"/>
+      <c r="G232" s="15"/>
       <c r="H232" s="10" t="str">
-        <f>IF(OR(G232="",E232="",F232=""),"",G232*F232*1000/E232)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I232" s="10" t="str">
-        <f>IF(E232="","",1000/E232)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J232" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K232" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A233" s="16"/>
-      <c r="B233" s="16"/>
-      <c r="C233" s="16"/>
-      <c r="D233" s="16"/>
-      <c r="E233" s="16"/>
-      <c r="F233" s="16"/>
-      <c r="G233" s="16"/>
+      <c r="A233" s="15"/>
+      <c r="B233" s="15"/>
+      <c r="C233" s="15"/>
+      <c r="D233" s="15"/>
+      <c r="E233" s="15"/>
+      <c r="F233" s="15"/>
+      <c r="G233" s="15"/>
       <c r="H233" s="10" t="str">
-        <f>IF(OR(G233="",E233="",F233=""),"",G233*F233*1000/E233)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I233" s="10" t="str">
-        <f>IF(E233="","",1000/E233)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J233" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K233" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A234" s="16"/>
-      <c r="B234" s="16"/>
-      <c r="C234" s="16"/>
-      <c r="D234" s="16"/>
-      <c r="E234" s="16"/>
-      <c r="F234" s="16"/>
-      <c r="G234" s="16"/>
+      <c r="A234" s="15"/>
+      <c r="B234" s="15"/>
+      <c r="C234" s="15"/>
+      <c r="D234" s="15"/>
+      <c r="E234" s="15"/>
+      <c r="F234" s="15"/>
+      <c r="G234" s="15"/>
       <c r="H234" s="10" t="str">
-        <f>IF(OR(G234="",E234="",F234=""),"",G234*F234*1000/E234)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I234" s="10" t="str">
-        <f>IF(E234="","",1000/E234)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J234" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K234" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A235" s="16"/>
-      <c r="B235" s="16"/>
-      <c r="C235" s="16"/>
-      <c r="D235" s="16"/>
-      <c r="E235" s="16"/>
-      <c r="F235" s="16"/>
-      <c r="G235" s="16"/>
+      <c r="A235" s="15"/>
+      <c r="B235" s="15"/>
+      <c r="C235" s="15"/>
+      <c r="D235" s="15"/>
+      <c r="E235" s="15"/>
+      <c r="F235" s="15"/>
+      <c r="G235" s="15"/>
       <c r="H235" s="10" t="str">
-        <f>IF(OR(G235="",E235="",F235=""),"",G235*F235*1000/E235)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I235" s="10" t="str">
-        <f>IF(E235="","",1000/E235)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J235" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K235" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A236" s="16"/>
-      <c r="B236" s="16"/>
-      <c r="C236" s="16"/>
-      <c r="D236" s="16"/>
-      <c r="E236" s="16"/>
-      <c r="F236" s="16"/>
-      <c r="G236" s="16"/>
+      <c r="A236" s="15"/>
+      <c r="B236" s="15"/>
+      <c r="C236" s="15"/>
+      <c r="D236" s="15"/>
+      <c r="E236" s="15"/>
+      <c r="F236" s="15"/>
+      <c r="G236" s="15"/>
       <c r="H236" s="10" t="str">
-        <f>IF(OR(G236="",E236="",F236=""),"",G236*F236*1000/E236)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I236" s="10" t="str">
-        <f>IF(E236="","",1000/E236)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J236" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K236" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A237" s="16"/>
-      <c r="B237" s="16"/>
-      <c r="C237" s="16"/>
-      <c r="D237" s="16"/>
-      <c r="E237" s="16"/>
-      <c r="F237" s="16"/>
-      <c r="G237" s="16"/>
+      <c r="A237" s="15"/>
+      <c r="B237" s="15"/>
+      <c r="C237" s="15"/>
+      <c r="D237" s="15"/>
+      <c r="E237" s="15"/>
+      <c r="F237" s="15"/>
+      <c r="G237" s="15"/>
       <c r="H237" s="10" t="str">
-        <f>IF(OR(G237="",E237="",F237=""),"",G237*F237*1000/E237)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I237" s="10" t="str">
-        <f>IF(E237="","",1000/E237)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J237" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K237" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A238" s="16"/>
-      <c r="B238" s="16"/>
-      <c r="C238" s="16"/>
-      <c r="D238" s="16"/>
-      <c r="E238" s="16"/>
-      <c r="F238" s="16"/>
-      <c r="G238" s="16"/>
+      <c r="A238" s="15"/>
+      <c r="B238" s="15"/>
+      <c r="C238" s="15"/>
+      <c r="D238" s="15"/>
+      <c r="E238" s="15"/>
+      <c r="F238" s="15"/>
+      <c r="G238" s="15"/>
       <c r="H238" s="10" t="str">
-        <f>IF(OR(G238="",E238="",F238=""),"",G238*F238*1000/E238)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I238" s="10" t="str">
-        <f>IF(E238="","",1000/E238)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J238" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K238" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A239" s="16"/>
-      <c r="B239" s="16"/>
-      <c r="C239" s="16"/>
-      <c r="D239" s="16"/>
-      <c r="E239" s="16"/>
-      <c r="F239" s="16"/>
-      <c r="G239" s="16"/>
+      <c r="A239" s="15"/>
+      <c r="B239" s="15"/>
+      <c r="C239" s="15"/>
+      <c r="D239" s="15"/>
+      <c r="E239" s="15"/>
+      <c r="F239" s="15"/>
+      <c r="G239" s="15"/>
       <c r="H239" s="10" t="str">
-        <f>IF(OR(G239="",E239="",F239=""),"",G239*F239*1000/E239)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I239" s="10" t="str">
-        <f>IF(E239="","",1000/E239)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J239" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K239" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A240" s="16"/>
-      <c r="B240" s="16"/>
-      <c r="C240" s="16"/>
-      <c r="D240" s="16"/>
-      <c r="E240" s="16"/>
-      <c r="F240" s="16"/>
-      <c r="G240" s="16"/>
+      <c r="A240" s="15"/>
+      <c r="B240" s="15"/>
+      <c r="C240" s="15"/>
+      <c r="D240" s="15"/>
+      <c r="E240" s="15"/>
+      <c r="F240" s="15"/>
+      <c r="G240" s="15"/>
       <c r="H240" s="10" t="str">
-        <f>IF(OR(G240="",E240="",F240=""),"",G240*F240*1000/E240)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I240" s="10" t="str">
-        <f>IF(E240="","",1000/E240)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J240" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K240" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A241" s="16"/>
-      <c r="B241" s="16"/>
-      <c r="C241" s="16"/>
-      <c r="D241" s="16"/>
-      <c r="E241" s="16"/>
-      <c r="F241" s="16"/>
-      <c r="G241" s="16"/>
+      <c r="A241" s="15"/>
+      <c r="B241" s="15"/>
+      <c r="C241" s="15"/>
+      <c r="D241" s="15"/>
+      <c r="E241" s="15"/>
+      <c r="F241" s="15"/>
+      <c r="G241" s="15"/>
       <c r="H241" s="10" t="str">
-        <f>IF(OR(G241="",E241="",F241=""),"",G241*F241*1000/E241)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I241" s="10" t="str">
-        <f>IF(E241="","",1000/E241)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J241" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K241" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A242" s="16"/>
-      <c r="B242" s="16"/>
-      <c r="C242" s="16"/>
-      <c r="D242" s="16"/>
-      <c r="E242" s="16"/>
-      <c r="F242" s="16"/>
-      <c r="G242" s="16"/>
+      <c r="A242" s="15"/>
+      <c r="B242" s="15"/>
+      <c r="C242" s="15"/>
+      <c r="D242" s="15"/>
+      <c r="E242" s="15"/>
+      <c r="F242" s="15"/>
+      <c r="G242" s="15"/>
       <c r="H242" s="10" t="str">
-        <f>IF(OR(G242="",E242="",F242=""),"",G242*F242*1000/E242)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I242" s="10" t="str">
-        <f>IF(E242="","",1000/E242)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J242" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K242" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A243" s="16"/>
-      <c r="B243" s="16"/>
-      <c r="C243" s="16"/>
-      <c r="D243" s="16"/>
-      <c r="E243" s="16"/>
-      <c r="F243" s="16"/>
-      <c r="G243" s="16"/>
+      <c r="A243" s="15"/>
+      <c r="B243" s="15"/>
+      <c r="C243" s="15"/>
+      <c r="D243" s="15"/>
+      <c r="E243" s="15"/>
+      <c r="F243" s="15"/>
+      <c r="G243" s="15"/>
       <c r="H243" s="10" t="str">
-        <f>IF(OR(G243="",E243="",F243=""),"",G243*F243*1000/E243)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I243" s="10" t="str">
-        <f>IF(E243="","",1000/E243)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J243" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K243" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A244" s="16"/>
-      <c r="B244" s="16"/>
-      <c r="C244" s="16"/>
-      <c r="D244" s="16"/>
-      <c r="E244" s="16"/>
-      <c r="F244" s="16"/>
-      <c r="G244" s="16"/>
+      <c r="A244" s="15"/>
+      <c r="B244" s="15"/>
+      <c r="C244" s="15"/>
+      <c r="D244" s="15"/>
+      <c r="E244" s="15"/>
+      <c r="F244" s="15"/>
+      <c r="G244" s="15"/>
       <c r="H244" s="10" t="str">
-        <f>IF(OR(G244="",E244="",F244=""),"",G244*F244*1000/E244)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I244" s="10" t="str">
-        <f>IF(E244="","",1000/E244)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J244" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K244" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -10600,7 +10422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -10614,48 +10436,46 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B5" s="6" t="str">
         <f>Design!B15</f>
         <v>50000</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <f>AVERAGE(Counts!H5:H8,Counts!H29:H32,Counts!H53:H56)</f>
         <v>50833.333333333336</v>
       </c>
@@ -10674,13 +10494,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B6" s="6" t="str">
         <f>Design!B16</f>
         <v>500000</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="16">
         <f>AVERAGE(Counts!H77:H80,Counts!H101:H104,Counts!H125:H128)</f>
         <v>501666.66666666669</v>
       </c>
@@ -10699,13 +10519,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B7" s="6" t="str">
         <f>Design!B17</f>
         <v>5000000</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="16">
         <f>AVERAGE(Counts!H149:H152,Counts!H173:H176,Counts!H197:H200)</f>
         <v>4975000</v>
       </c>
@@ -10723,14 +10543,12 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
